--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>87493</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>6.78000020980835</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>6.78000020980835</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>6.73000001907349</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>145616</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>6.71000003814697</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>6.53999996185303</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>6.71000003814697</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>6.53000020980835</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -62920,7 +62920,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="D2720" t="n">
-        <v>6.53999996185303</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="E2720" t="n">
         <v>6.71000003814697</v>
@@ -62929,6 +62929,29 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>79278</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>6.73999977111816</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>6.51999998092651</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>6.51999998092651</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>6.69000005722046</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>52009</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>6.73999977111816</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>6.6399998664856</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>6.73000001907349</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>6.65000009536743</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>119420</v>
+        <v>42823</v>
       </c>
       <c r="C2715" t="n">
-        <v>6.92000007629395</v>
+        <v>7.03999996185303</v>
       </c>
       <c r="D2715" t="n">
-        <v>6.80000019073486</v>
+        <v>6.92999982833862</v>
       </c>
       <c r="E2715" t="n">
-        <v>6.92000007629395</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="F2715" t="n">
-        <v>6.80000019073486</v>
+        <v>6.92999982833862</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>221546</v>
+        <v>119420</v>
       </c>
       <c r="C2716" t="n">
+        <v>6.92000007629395</v>
+      </c>
+      <c r="D2716" t="n">
         <v>6.80000019073486</v>
       </c>
-      <c r="D2716" t="n">
-        <v>6.63000011444092</v>
-      </c>
       <c r="E2716" t="n">
+        <v>6.92000007629395</v>
+      </c>
+      <c r="F2716" t="n">
         <v>6.80000019073486</v>
-      </c>
-      <c r="F2716" t="n">
-        <v>6.73000001907349</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>56659</v>
+        <v>221546</v>
       </c>
       <c r="C2717" t="n">
-        <v>6.80999994277954</v>
+        <v>6.80000019073486</v>
       </c>
       <c r="D2717" t="n">
-        <v>6.69999980926514</v>
+        <v>6.63000011444092</v>
       </c>
       <c r="E2717" t="n">
-        <v>6.80999994277954</v>
+        <v>6.80000019073486</v>
       </c>
       <c r="F2717" t="n">
-        <v>6.71000003814697</v>
+        <v>6.73000001907349</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>73199</v>
+        <v>56659</v>
       </c>
       <c r="C2718" t="n">
-        <v>6.76000022888184</v>
+        <v>6.80999994277954</v>
       </c>
       <c r="D2718" t="n">
-        <v>6.69000005722046</v>
+        <v>6.69999980926514</v>
       </c>
       <c r="E2718" t="n">
-        <v>6.73000001907349</v>
+        <v>6.80999994277954</v>
       </c>
       <c r="F2718" t="n">
-        <v>6.69999980926514</v>
+        <v>6.71000003814697</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>87493</v>
+        <v>73199</v>
       </c>
       <c r="C2719" t="n">
-        <v>6.78000020980835</v>
+        <v>6.76000022888184</v>
       </c>
       <c r="D2719" t="n">
-        <v>6.65999984741211</v>
+        <v>6.69000005722046</v>
       </c>
       <c r="E2719" t="n">
-        <v>6.78000020980835</v>
+        <v>6.73000001907349</v>
       </c>
       <c r="F2719" t="n">
-        <v>6.73000001907349</v>
+        <v>6.69999980926514</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>145616</v>
+        <v>87493</v>
       </c>
       <c r="C2720" t="n">
-        <v>6.71000003814697</v>
+        <v>6.78000020980835</v>
       </c>
       <c r="D2720" t="n">
-        <v>6.53000020980835</v>
+        <v>6.65999984741211</v>
       </c>
       <c r="E2720" t="n">
-        <v>6.71000003814697</v>
+        <v>6.78000020980835</v>
       </c>
       <c r="F2720" t="n">
-        <v>6.53000020980835</v>
+        <v>6.73000001907349</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>79278</v>
+        <v>145616</v>
       </c>
       <c r="C2721" t="n">
-        <v>6.73999977111816</v>
+        <v>6.71000003814697</v>
       </c>
       <c r="D2721" t="n">
-        <v>6.51999998092651</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="E2721" t="n">
-        <v>6.51999998092651</v>
+        <v>6.71000003814697</v>
       </c>
       <c r="F2721" t="n">
-        <v>6.69000005722046</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>52009</v>
+        <v>79278</v>
       </c>
       <c r="C2722" t="n">
         <v>6.73999977111816</v>
       </c>
       <c r="D2722" t="n">
-        <v>6.6399998664856</v>
+        <v>6.51999998092651</v>
       </c>
       <c r="E2722" t="n">
-        <v>6.73000001907349</v>
+        <v>6.51999998092651</v>
       </c>
       <c r="F2722" t="n">
-        <v>6.65000009536743</v>
+        <v>6.69000005722046</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>103507</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>6.59000015258789</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G2" t="n">
-        <v>3.92318487167358</v>
+        <v>3.923184633255</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.90674161911011</v>
+        <v>3.90674185752869</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G4" t="n">
-        <v>3.82452964782715</v>
+        <v>3.82452917098999</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>3.71600842475891</v>
+        <v>3.71600818634033</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G7" t="n">
-        <v>3.60091114044189</v>
+        <v>3.60091066360474</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>3.64695000648499</v>
+        <v>3.64695024490356</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.63379645347595</v>
+        <v>3.63379621505737</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G10" t="n">
-        <v>3.68970131874084</v>
+        <v>3.68970060348511</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>3.66010427474976</v>
+        <v>3.66010403633118</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.57789134979248</v>
+        <v>3.57789206504822</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>3.55816078186035</v>
+        <v>3.55816006660461</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45950531959534</v>
+        <v>3.45950555801392</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G15" t="n">
-        <v>3.545006275177</v>
+        <v>3.54500603675842</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.61735391616821</v>
+        <v>3.61735343933105</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.5</v>
       </c>
       <c r="G17" t="n">
-        <v>3.61735391616821</v>
+        <v>3.61735343933105</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.59433436393738</v>
+        <v>3.5943341255188</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>3.55158281326294</v>
+        <v>3.55158352851868</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>3.55158281326294</v>
+        <v>3.55158352851868</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G21" t="n">
-        <v>3.58446931838989</v>
+        <v>3.584468126297</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G22" t="n">
-        <v>3.63708472251892</v>
+        <v>3.63708519935608</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.5</v>
       </c>
       <c r="G23" t="n">
-        <v>3.61735391616821</v>
+        <v>3.61735343933105</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>3.49239039421082</v>
+        <v>3.49238991737366</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>3.48581337928772</v>
+        <v>3.4858136177063</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>3.47923636436462</v>
+        <v>3.4792366027832</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.41346645355225</v>
+        <v>3.41346669197083</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>3.28850293159485</v>
+        <v>3.28850317001343</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G31" t="n">
-        <v>3.30823421478271</v>
+        <v>3.30823445320129</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G32" t="n">
-        <v>3.40688943862915</v>
+        <v>3.40688920021057</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.25</v>
       </c>
       <c r="G33" t="n">
-        <v>3.45292806625366</v>
+        <v>3.45292854309082</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>3.46279382705688</v>
+        <v>3.46279358863831</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>3.48581337928772</v>
+        <v>3.4858136177063</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>3.49239039421082</v>
+        <v>3.49238991737366</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50554394721985</v>
+        <v>3.50554418563843</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G38" t="n">
-        <v>3.47265934944153</v>
+        <v>3.47265982627869</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G39" t="n">
-        <v>3.41346645355225</v>
+        <v>3.41346669197083</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42333149909973</v>
+        <v>3.42333173751831</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.45621681213379</v>
+        <v>3.45621728897095</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.47594833374023</v>
+        <v>3.4759476184845</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>3.49567890167236</v>
+        <v>3.49567914009094</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>3.47923636436462</v>
+        <v>3.4792366027832</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G47" t="n">
-        <v>3.43977451324463</v>
+        <v>3.43977427482605</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.25</v>
       </c>
       <c r="G48" t="n">
-        <v>3.45292806625366</v>
+        <v>3.45292854309082</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>3.46608233451843</v>
+        <v>3.46608185768127</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G50" t="n">
-        <v>3.48581337928772</v>
+        <v>3.4858136177063</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>3.53842949867249</v>
+        <v>3.53842973709106</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>3.72916197776794</v>
+        <v>3.72916293144226</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G55" t="n">
-        <v>3.75218152999878</v>
+        <v>3.7521824836731</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>3.73902797698975</v>
+        <v>3.73902869224548</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>3.81466388702393</v>
+        <v>3.81466436386108</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G58" t="n">
-        <v>3.82124018669128</v>
+        <v>3.82124066352844</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.80150961875916</v>
+        <v>3.80151009559631</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.80808639526367</v>
+        <v>3.80808615684509</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>3.80150961875916</v>
+        <v>3.80151009559631</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G64" t="n">
-        <v>3.79493379592896</v>
+        <v>3.79493284225464</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G66" t="n">
-        <v>3.82452964782715</v>
+        <v>3.82452917098999</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>3.76533603668213</v>
+        <v>3.76533532142639</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G69" t="n">
-        <v>3.82124018669128</v>
+        <v>3.82124066352844</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G71" t="n">
-        <v>3.81466388702393</v>
+        <v>3.81466436386108</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.75500011444092</v>
       </c>
       <c r="G73" t="n">
-        <v>3.78506684303284</v>
+        <v>3.78506827354431</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G76" t="n">
-        <v>3.81466388702393</v>
+        <v>3.81466436386108</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>3.82452964782715</v>
+        <v>3.82452917098999</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.84754872322083</v>
+        <v>3.84754848480225</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.79822206497192</v>
+        <v>3.79822039604187</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>3.81466388702393</v>
+        <v>3.81466436386108</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.85741400718689</v>
+        <v>3.85741376876831</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.75500011444092</v>
       </c>
       <c r="G86" t="n">
-        <v>3.78506684303284</v>
+        <v>3.78506827354431</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G87" t="n">
-        <v>3.80150961875916</v>
+        <v>3.80151009559631</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>3.75875973701477</v>
+        <v>3.75875854492188</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.73902797698975</v>
+        <v>3.73902869224548</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.5</v>
       </c>
       <c r="G90" t="n">
-        <v>3.7733314037323</v>
+        <v>3.77333116531372</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>3.75960969924927</v>
+        <v>3.75961017608643</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.74588847160339</v>
+        <v>3.74588823318481</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.5</v>
       </c>
       <c r="G94" t="n">
-        <v>3.7733314037323</v>
+        <v>3.77333116531372</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.74931955337524</v>
+        <v>3.74931931495667</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>3.76304054260254</v>
+        <v>3.76304006576538</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G97" t="n">
-        <v>3.78019094467163</v>
+        <v>3.78019189834595</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>3.78705191612244</v>
+        <v>3.78705239295959</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G99" t="n">
-        <v>3.77676153182983</v>
+        <v>3.77676105499268</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.8282163143158</v>
+        <v>3.82821607589722</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G101" t="n">
-        <v>3.83850622177124</v>
+        <v>3.8385066986084</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.84536719322205</v>
+        <v>3.8453676700592</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>3.96885776519775</v>
+        <v>3.96885848045349</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96885776519775</v>
+        <v>3.96885848045349</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>3.93798494338989</v>
+        <v>3.93798518180847</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.92083501815796</v>
+        <v>3.92083358764648</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87623953819275</v>
+        <v>3.87623977661133</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>3.8899610042572</v>
+        <v>3.88996124267578</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G113" t="n">
-        <v>3.85565876960754</v>
+        <v>3.85565853118896</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G114" t="n">
-        <v>3.75960969924927</v>
+        <v>3.75961017608643</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G115" t="n">
-        <v>3.69100379943848</v>
+        <v>3.69100403785706</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>3.67042207717896</v>
+        <v>3.6704216003418</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G117" t="n">
-        <v>3.64640998840332</v>
+        <v>3.64641046524048</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G118" t="n">
-        <v>3.63954925537109</v>
+        <v>3.63954901695251</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79048323631287</v>
+        <v>3.79048299789429</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G120" t="n">
-        <v>3.83850622177124</v>
+        <v>3.8385066986084</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>3.80763411521912</v>
+        <v>3.80763363838196</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>3.91740369796753</v>
+        <v>3.91740417480469</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>3.78019094467163</v>
+        <v>3.78019189834595</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.71844553947449</v>
+        <v>3.71844601631165</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>3.75960969924927</v>
+        <v>3.75961017608643</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>3.74588847160339</v>
+        <v>3.74588823318481</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.71158599853516</v>
+        <v>3.71158528327942</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G132" t="n">
-        <v>3.69443416595459</v>
+        <v>3.69443440437317</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G133" t="n">
-        <v>3.72873663902283</v>
+        <v>3.72873711585999</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>3.73902893066406</v>
+        <v>3.73902773857117</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.70472455024719</v>
+        <v>3.70472526550293</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>3.75274896621704</v>
+        <v>3.75274920463562</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>3.71844553947449</v>
+        <v>3.71844601631165</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G138" t="n">
-        <v>3.78019094467163</v>
+        <v>3.78019189834595</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G139" t="n">
-        <v>3.78362107276917</v>
+        <v>3.78362154960632</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G140" t="n">
-        <v>3.82135510444641</v>
+        <v>3.82135558128357</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G141" t="n">
-        <v>3.79391312599182</v>
+        <v>3.79391288757324</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G142" t="n">
-        <v>3.83850622177124</v>
+        <v>3.8385066986084</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>3.80077314376831</v>
+        <v>3.80077409744263</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>3.86251854896545</v>
+        <v>3.86251902580261</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>3.80763411521912</v>
+        <v>3.80763363838196</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G147" t="n">
-        <v>3.88310098648071</v>
+        <v>3.88310050964355</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G148" t="n">
-        <v>3.90368223190308</v>
+        <v>3.9036819934845</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G149" t="n">
-        <v>3.84193682670593</v>
+        <v>3.84193634986877</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G150" t="n">
-        <v>3.78362107276917</v>
+        <v>3.78362154960632</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>3.73902893066406</v>
+        <v>3.73902773857117</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>3.73216772079468</v>
+        <v>3.7321674823761</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G153" t="n">
-        <v>3.71158599853516</v>
+        <v>3.71158528327942</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.70129489898682</v>
+        <v>3.7012951374054</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>3.71844553947449</v>
+        <v>3.71844601631165</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G156" t="n">
-        <v>3.71158599853516</v>
+        <v>3.71158528327942</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>3.70472455024719</v>
+        <v>3.70472526550293</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>3.70472455024719</v>
+        <v>3.70472526550293</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G160" t="n">
-        <v>3.67042207717896</v>
+        <v>3.6704216003418</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>3.71158599853516</v>
+        <v>3.71158528327942</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G163" t="n">
-        <v>3.65670084953308</v>
+        <v>3.6567006111145</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>3.65327072143555</v>
+        <v>3.65326976776123</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G165" t="n">
-        <v>3.65670084953308</v>
+        <v>3.6567006111145</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G166" t="n">
-        <v>3.65670084953308</v>
+        <v>3.6567006111145</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G167" t="n">
-        <v>3.65670084953308</v>
+        <v>3.6567006111145</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>3.65670084953308</v>
+        <v>3.6567006111145</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>3.61553716659546</v>
+        <v>3.61553692817688</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G173" t="n">
-        <v>3.63954925537109</v>
+        <v>3.63954901695251</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G174" t="n">
-        <v>3.66356229782104</v>
+        <v>3.66356205940247</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G175" t="n">
-        <v>3.71158599853516</v>
+        <v>3.71158528327942</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G176" t="n">
-        <v>3.67728304862976</v>
+        <v>3.6772825717926</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G177" t="n">
-        <v>3.70815515518188</v>
+        <v>3.70815563201904</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.65670084953308</v>
+        <v>3.6567006111145</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>3.65670084953308</v>
+        <v>3.6567006111145</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.61896777153015</v>
+        <v>3.61896753311157</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G181" t="n">
-        <v>3.62925839424133</v>
+        <v>3.62925887107849</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62239789962769</v>
+        <v>3.62239813804626</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G184" t="n">
-        <v>3.66356229782104</v>
+        <v>3.66356205940247</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G186" t="n">
-        <v>3.62239789962769</v>
+        <v>3.62239813804626</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G188" t="n">
-        <v>3.63954925537109</v>
+        <v>3.63954901695251</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>3.54693126678467</v>
+        <v>3.54693078994751</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.51262784004211</v>
+        <v>3.51262807846069</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G194" t="n">
-        <v>3.51262784004211</v>
+        <v>3.51262807846069</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G197" t="n">
-        <v>3.50919795036316</v>
+        <v>3.50919723510742</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>3.63268852233887</v>
+        <v>3.63268804550171</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G200" t="n">
-        <v>3.76304054260254</v>
+        <v>3.76304006576538</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G201" t="n">
-        <v>3.73216772079468</v>
+        <v>3.7321674823761</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G202" t="n">
-        <v>3.71844553947449</v>
+        <v>3.71844601631165</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>3.74931955337524</v>
+        <v>3.74931931495667</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>3.80763411521912</v>
+        <v>3.80763363838196</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G205" t="n">
-        <v>3.80763411521912</v>
+        <v>3.80763363838196</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G206" t="n">
-        <v>3.804203748703</v>
+        <v>3.80420327186584</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>3.8282163143158</v>
+        <v>3.82821607589722</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G208" t="n">
-        <v>3.86937999725342</v>
+        <v>3.8693790435791</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G209" t="n">
-        <v>3.87967038154602</v>
+        <v>3.8796706199646</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G210" t="n">
-        <v>3.87967038154602</v>
+        <v>3.8796706199646</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>3.79048323631287</v>
+        <v>3.79048299789429</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>3.77676153182983</v>
+        <v>3.77676105499268</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>3.78362107276917</v>
+        <v>3.78362154960632</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G215" t="n">
-        <v>3.76646995544434</v>
+        <v>3.76647067070007</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>3.76990079879761</v>
+        <v>3.76990103721619</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G217" t="n">
-        <v>3.78362107276917</v>
+        <v>3.78362154960632</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G218" t="n">
-        <v>3.76646995544434</v>
+        <v>3.76647067070007</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>3.76646995544434</v>
+        <v>3.76647067070007</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G220" t="n">
-        <v>3.68414306640625</v>
+        <v>3.68414330482483</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73902893066406</v>
+        <v>3.73902773857117</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G223" t="n">
-        <v>3.74931955337524</v>
+        <v>3.74931931495667</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G224" t="n">
-        <v>3.68071269989014</v>
+        <v>3.68071341514587</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G225" t="n">
-        <v>3.71158599853516</v>
+        <v>3.71158528327942</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G226" t="n">
-        <v>3.73559832572937</v>
+        <v>3.73559808731079</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>3.70129489898682</v>
+        <v>3.7012951374054</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G228" t="n">
-        <v>3.66356229782104</v>
+        <v>3.66356205940247</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.25</v>
       </c>
       <c r="G229" t="n">
-        <v>3.60181593894958</v>
+        <v>3.60181570053101</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G231" t="n">
-        <v>3.68414306640625</v>
+        <v>3.68414330482483</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G232" t="n">
-        <v>3.71158599853516</v>
+        <v>3.71158528327942</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>3.70472455024719</v>
+        <v>3.70472526550293</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G234" t="n">
-        <v>3.64640998840332</v>
+        <v>3.64641046524048</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>3.70129489898682</v>
+        <v>3.7012951374054</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>3.65327072143555</v>
+        <v>3.65326976776123</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.25</v>
       </c>
       <c r="G238" t="n">
-        <v>3.60181593894958</v>
+        <v>3.60181570053101</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>3.65670084953308</v>
+        <v>3.6567006111145</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G240" t="n">
-        <v>3.69443416595459</v>
+        <v>3.69443440437317</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.80077314376831</v>
+        <v>3.80077409744263</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>3.804203748703</v>
+        <v>3.80420327186584</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G243" t="n">
-        <v>3.79391312599182</v>
+        <v>3.79391288757324</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>3.78705191612244</v>
+        <v>3.78705239295959</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>3.78705191612244</v>
+        <v>3.78705239295959</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G246" t="n">
-        <v>3.76304054260254</v>
+        <v>3.76304006576538</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G248" t="n">
-        <v>3.79391312599182</v>
+        <v>3.79391288757324</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.76646995544434</v>
+        <v>3.76647067070007</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G250" t="n">
-        <v>3.74245810508728</v>
+        <v>3.7424578666687</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>3.76646995544434</v>
+        <v>3.76647067070007</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>3.74588847160339</v>
+        <v>3.74588823318481</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G254" t="n">
-        <v>3.76646995544434</v>
+        <v>3.76647067070007</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G255" t="n">
-        <v>3.73559832572937</v>
+        <v>3.73559808731079</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.74931955337524</v>
+        <v>3.74931931495667</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>3.78705191612244</v>
+        <v>3.78705239295959</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>3.84193682670593</v>
+        <v>3.84193634986877</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>3.91397309303284</v>
+        <v>3.91397333145142</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G260" t="n">
-        <v>3.87967038154602</v>
+        <v>3.8796706199646</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G261" t="n">
-        <v>3.92426419258118</v>
+        <v>3.9242639541626</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>3.91740369796753</v>
+        <v>3.91740417480469</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G263" t="n">
-        <v>3.96542811393738</v>
+        <v>3.96542835235596</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>3.97914910316467</v>
+        <v>3.97914958000183</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G265" t="n">
-        <v>3.93455600738525</v>
+        <v>3.93455529212952</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>3.97228813171387</v>
+        <v>3.97228837013245</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G268" t="n">
-        <v>3.97228813171387</v>
+        <v>3.97228837013245</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G269" t="n">
-        <v>3.98944044113159</v>
+        <v>3.98943996429443</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G270" t="n">
-        <v>3.96542811393738</v>
+        <v>3.96542835235596</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95856833457947</v>
+        <v>3.95856761932373</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.7649998664856</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95513677597046</v>
+        <v>3.95513725280762</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G273" t="n">
-        <v>3.88310098648071</v>
+        <v>3.88310050964355</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G274" t="n">
-        <v>3.84193682670593</v>
+        <v>3.84193634986877</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>3.91740369796753</v>
+        <v>3.91740417480469</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>3.90368223190308</v>
+        <v>3.9036819934845</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G277" t="n">
-        <v>3.93798494338989</v>
+        <v>3.93798518180847</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>3.91740369796753</v>
+        <v>3.91740417480469</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G280" t="n">
-        <v>3.85565876960754</v>
+        <v>3.85565853118896</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>3.84193682670593</v>
+        <v>3.84193634986877</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G283" t="n">
-        <v>3.86937999725342</v>
+        <v>3.8693790435791</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>3.87623953819275</v>
+        <v>3.87623977661133</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G285" t="n">
-        <v>3.92769455909729</v>
+        <v>3.92769408226013</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>3.95856833457947</v>
+        <v>3.95856761932373</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>4.01345205307007</v>
+        <v>4.01345157623291</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.98944044113159</v>
+        <v>3.98943996429443</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>4.01345205307007</v>
+        <v>4.01345157623291</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G294" t="n">
-        <v>3.98944044113159</v>
+        <v>3.98943996429443</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G295" t="n">
-        <v>4.04775524139404</v>
+        <v>4.04775476455688</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>4.04775524139404</v>
+        <v>4.04775476455688</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>4.06147623062134</v>
+        <v>4.0614767074585</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G298" t="n">
-        <v>4.06147623062134</v>
+        <v>4.0614767074585</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G301" t="n">
-        <v>4.09234952926636</v>
+        <v>4.0923490524292</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G303" t="n">
-        <v>4.15066432952881</v>
+        <v>4.15066385269165</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>4.15066432952881</v>
+        <v>4.15066385269165</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G306" t="n">
-        <v>4.23985195159912</v>
+        <v>4.23985242843628</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G307" t="n">
-        <v>4.22613143920898</v>
+        <v>4.22613048553467</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G308" t="n">
-        <v>4.18496751785278</v>
+        <v>4.18496704101562</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G310" t="n">
-        <v>4.23985195159912</v>
+        <v>4.23985242843628</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.25357341766357</v>
+        <v>4.25357389450073</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>4.3770637512207</v>
+        <v>4.37706470489502</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>4.7681188583374</v>
+        <v>4.76811838150024</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>7</v>
       </c>
       <c r="G315" t="n">
-        <v>4.80242109298706</v>
+        <v>4.80242156982422</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G317" t="n">
-        <v>5.069983959198</v>
+        <v>5.06998491287231</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>5.07684564590454</v>
+        <v>5.07684516906738</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.07684564590454</v>
+        <v>5.07684516906738</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G322" t="n">
-        <v>4.92591190338135</v>
+        <v>4.92591142654419</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.95678472518921</v>
+        <v>4.95678520202637</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>5.00823926925659</v>
+        <v>5.00824022293091</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>5.069983959198</v>
+        <v>5.06998491287231</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02196073532104</v>
+        <v>5.0219612121582</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>5.07684564590454</v>
+        <v>5.07684516906738</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G334" t="n">
-        <v>4.99451780319214</v>
+        <v>4.99451875686646</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>5.09399747848511</v>
+        <v>5.09399700164795</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G337" t="n">
-        <v>5.11457920074463</v>
+        <v>5.11457824707031</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G339" t="n">
-        <v>5.35127019882202</v>
+        <v>5.35126876831055</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>5.20033597946167</v>
+        <v>5.20033550262451</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>7.75</v>
       </c>
       <c r="G341" t="n">
-        <v>5.31696653366089</v>
+        <v>5.31696701049805</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>5.28266429901123</v>
+        <v>5.28266382217407</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>5.36842107772827</v>
+        <v>5.36842155456543</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G348" t="n">
-        <v>5.45845031738281</v>
+        <v>5.4584493637085</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G349" t="n">
-        <v>5.45490550994873</v>
+        <v>5.45490598678589</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G353" t="n">
-        <v>5.25996017456055</v>
+        <v>5.25996065139771</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>5.30249452590942</v>
+        <v>5.30249357223511</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.29540586471558</v>
+        <v>5.29540491104126</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G361" t="n">
-        <v>5.21742725372314</v>
+        <v>5.2174277305603</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G362" t="n">
-        <v>5.27413892745972</v>
+        <v>5.2741379737854</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>5.24578285217285</v>
+        <v>5.24578332901001</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>5.30249452590942</v>
+        <v>5.30249357223511</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.5</v>
       </c>
       <c r="G365" t="n">
-        <v>5.31667280197144</v>
+        <v>5.31667184829712</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>5.28831624984741</v>
+        <v>5.28831672668457</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G370" t="n">
-        <v>5.38401651382446</v>
+        <v>5.38401699066162</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G371" t="n">
-        <v>5.45845031738281</v>
+        <v>5.4584493637085</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G372" t="n">
-        <v>5.43718242645264</v>
+        <v>5.43718290328979</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>5.25287199020386</v>
+        <v>5.2528715133667</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G381" t="n">
-        <v>5.34502744674683</v>
+        <v>5.34502696990967</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G383" t="n">
-        <v>5.1890721321106</v>
+        <v>5.18907260894775</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.13236045837402</v>
+        <v>5.13235998153687</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G387" t="n">
-        <v>5.0047607421875</v>
+        <v>5.00476026535034</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G389" t="n">
-        <v>5.11818313598633</v>
+        <v>5.11818265914917</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>4.99058294296265</v>
+        <v>4.99058198928833</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G392" t="n">
-        <v>5.27413892745972</v>
+        <v>5.2741379737854</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>5.24932718276978</v>
+        <v>5.24932765960693</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G396" t="n">
-        <v>5.08982706069946</v>
+        <v>5.0898265838623</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G398" t="n">
-        <v>5.30958318710327</v>
+        <v>5.30958271026611</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>5.25641632080078</v>
+        <v>5.25641679763794</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G400" t="n">
-        <v>5.26704931259155</v>
+        <v>5.26704978942871</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>5.25641632080078</v>
+        <v>5.25641679763794</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>5.19616079330444</v>
+        <v>5.19616031646729</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G405" t="n">
-        <v>5.32730436325073</v>
+        <v>5.32730531692505</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>5.34148263931274</v>
+        <v>5.34148359298706</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>5.45845031738281</v>
+        <v>5.4584493637085</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>5.45845031738281</v>
+        <v>5.4584493637085</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>5.4017391204834</v>
+        <v>5.40173864364624</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>5.25641632080078</v>
+        <v>5.25641679763794</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G415" t="n">
-        <v>5.35920572280884</v>
+        <v>5.35920524597168</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>5.37692737579346</v>
+        <v>5.37692785263062</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>5.24578285217285</v>
+        <v>5.24578332901001</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G421" t="n">
-        <v>5.42300510406494</v>
+        <v>5.4230055809021</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G423" t="n">
-        <v>5.35920572280884</v>
+        <v>5.35920524597168</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>5.34857177734375</v>
+        <v>5.34857225418091</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>5.30249452590942</v>
+        <v>5.30249357223511</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>5.44072723388672</v>
+        <v>5.44072771072388</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G434" t="n">
-        <v>5.34148263931274</v>
+        <v>5.34148359298706</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G436" t="n">
-        <v>5.42654943466187</v>
+        <v>5.42655038833618</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G443" t="n">
-        <v>5.77036142349243</v>
+        <v>5.77036094665527</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G444" t="n">
-        <v>5.82352876663208</v>
+        <v>5.82352781295776</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G445" t="n">
-        <v>5.82352876663208</v>
+        <v>5.82352781295776</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>5.81289482116699</v>
+        <v>5.81289386749268</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G450" t="n">
-        <v>5.71365022659302</v>
+        <v>5.71365070343018</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G451" t="n">
-        <v>5.66402721405029</v>
+        <v>5.66402769088745</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G452" t="n">
-        <v>5.78453922271729</v>
+        <v>5.78453826904297</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G453" t="n">
-        <v>5.71365022659302</v>
+        <v>5.71365070343018</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G455" t="n">
-        <v>5.73846101760864</v>
+        <v>5.7384614944458</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>5.61440563201904</v>
+        <v>5.61440658569336</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G461" t="n">
-        <v>5.68174982070923</v>
+        <v>5.68174934387207</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G464" t="n">
-        <v>5.6923828125</v>
+        <v>5.69238376617432</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>5.58605051040649</v>
+        <v>5.58605003356934</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G467" t="n">
-        <v>5.51870584487915</v>
+        <v>5.51870536804199</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G468" t="n">
-        <v>5.50098371505737</v>
+        <v>5.50098276138306</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>5.61086130142212</v>
+        <v>5.61086082458496</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G476" t="n">
-        <v>5.4442720413208</v>
+        <v>5.44427251815796</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G478" t="n">
-        <v>5.46553897857666</v>
+        <v>5.4655385017395</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>5.46199417114258</v>
+        <v>5.46199464797974</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>5.43718242645264</v>
+        <v>5.43718290328979</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>5.43718242645264</v>
+        <v>5.43718290328979</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.6356725692749</v>
+        <v>5.63567209243774</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G492" t="n">
-        <v>5.65339469909668</v>
+        <v>5.65339422225952</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>5.70656156539917</v>
+        <v>5.70656108856201</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G496" t="n">
-        <v>5.64984941482544</v>
+        <v>5.6498498916626</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G498" t="n">
-        <v>5.50098371505737</v>
+        <v>5.50098276138306</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.08500003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>5.73137187957764</v>
+        <v>5.73137140274048</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G500" t="n">
-        <v>5.75263833999634</v>
+        <v>5.7526388168335</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G502" t="n">
-        <v>5.77744960784912</v>
+        <v>5.77745008468628</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G503" t="n">
-        <v>5.77744960784912</v>
+        <v>5.77745008468628</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>5.77036142349243</v>
+        <v>5.77036094665527</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.81289482116699</v>
+        <v>5.81289386749268</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G507" t="n">
-        <v>5.81289482116699</v>
+        <v>5.81289386749268</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G508" t="n">
-        <v>5.78453922271729</v>
+        <v>5.78453826904297</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.25</v>
       </c>
       <c r="G509" t="n">
-        <v>5.84833908081055</v>
+        <v>5.84833955764771</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>5.88378429412842</v>
+        <v>5.88378381729126</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G511" t="n">
-        <v>5.77036142349243</v>
+        <v>5.77036094665527</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G512" t="n">
-        <v>5.83416080474854</v>
+        <v>5.83416032791138</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>5.81289482116699</v>
+        <v>5.81289386749268</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>5.91213989257812</v>
+        <v>5.91213798522949</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>5.88378429412842</v>
+        <v>5.88378381729126</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G516" t="n">
-        <v>5.88378429412842</v>
+        <v>5.88378381729126</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>5.91213989257812</v>
+        <v>5.91213798522949</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G519" t="n">
-        <v>6.00429534912109</v>
+        <v>6.00429487228394</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G520" t="n">
-        <v>5.91213989257812</v>
+        <v>5.91213798522949</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G521" t="n">
-        <v>5.88378429412842</v>
+        <v>5.88378381729126</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G522" t="n">
-        <v>5.85542869567871</v>
+        <v>5.85542821884155</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G523" t="n">
-        <v>5.85542869567871</v>
+        <v>5.85542821884155</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G524" t="n">
-        <v>5.86251735687256</v>
+        <v>5.8625168800354</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G525" t="n">
-        <v>5.86960601806641</v>
+        <v>5.86960554122925</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>8.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.02556228637695</v>
+        <v>6.02556180953979</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G529" t="n">
-        <v>5.96176099777222</v>
+        <v>5.96176052093506</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G530" t="n">
-        <v>5.94758319854736</v>
+        <v>5.94758367538452</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G531" t="n">
-        <v>5.94758319854736</v>
+        <v>5.94758367538452</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G532" t="n">
-        <v>5.88378429412842</v>
+        <v>5.88378381729126</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>5.6285834312439</v>
+        <v>5.62858295440674</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>5.46553897857666</v>
+        <v>5.4655385017395</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G541" t="n">
-        <v>5.77036142349243</v>
+        <v>5.77036094665527</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G542" t="n">
-        <v>5.77036142349243</v>
+        <v>5.77036094665527</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>5.79162740707397</v>
+        <v>5.79162788391113</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G544" t="n">
-        <v>5.77744960784912</v>
+        <v>5.77745008468628</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G546" t="n">
-        <v>5.72073936462402</v>
+        <v>5.72073888778687</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G547" t="n">
-        <v>5.77036142349243</v>
+        <v>5.77036094665527</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G548" t="n">
-        <v>5.72073936462402</v>
+        <v>5.72073888778687</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>5.79162740707397</v>
+        <v>5.79162788391113</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G550" t="n">
-        <v>5.67820596694946</v>
+        <v>5.6782054901123</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G552" t="n">
-        <v>5.81289482116699</v>
+        <v>5.81289386749268</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>5.81289482116699</v>
+        <v>5.81289386749268</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G554" t="n">
-        <v>5.77744960784912</v>
+        <v>5.77745008468628</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>5.70656156539917</v>
+        <v>5.70656108856201</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>5.71365022659302</v>
+        <v>5.71365070343018</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G557" t="n">
-        <v>5.79162740707397</v>
+        <v>5.79162788391113</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G558" t="n">
-        <v>5.86251735687256</v>
+        <v>5.8625168800354</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G561" t="n">
-        <v>5.96176099777222</v>
+        <v>5.96176052093506</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G562" t="n">
-        <v>5.97593927383423</v>
+        <v>5.97593975067139</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G563" t="n">
-        <v>5.91213989257812</v>
+        <v>5.91213798522949</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>5.88378429412842</v>
+        <v>5.88378381729126</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>5.88378429412842</v>
+        <v>5.88378381729126</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G568" t="n">
-        <v>5.85542869567871</v>
+        <v>5.85542821884155</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>5.78453922271729</v>
+        <v>5.78453826904297</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G571" t="n">
-        <v>5.83416080474854</v>
+        <v>5.83416032791138</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>5.88378429412842</v>
+        <v>5.88378381729126</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>5.88378429412842</v>
+        <v>5.88378381729126</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G575" t="n">
-        <v>5.97593927383423</v>
+        <v>5.97593975067139</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>5.96885013580322</v>
+        <v>5.96885061264038</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G578" t="n">
-        <v>5.85542869567871</v>
+        <v>5.85542821884155</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G579" t="n">
-        <v>5.86251735687256</v>
+        <v>5.8625168800354</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.25</v>
       </c>
       <c r="G580" t="n">
-        <v>5.84833908081055</v>
+        <v>5.84833955764771</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>5.84833908081055</v>
+        <v>5.84833955764771</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G583" t="n">
-        <v>5.86251735687256</v>
+        <v>5.8625168800354</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G584" t="n">
-        <v>5.77744960784912</v>
+        <v>5.77745008468628</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G585" t="n">
-        <v>5.85542869567871</v>
+        <v>5.85542821884155</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.25</v>
       </c>
       <c r="G586" t="n">
-        <v>5.84833908081055</v>
+        <v>5.84833955764771</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.25</v>
       </c>
       <c r="G587" t="n">
-        <v>5.84833908081055</v>
+        <v>5.84833955764771</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G590" t="n">
-        <v>5.91922807693481</v>
+        <v>5.91922855377197</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>5.8766942024231</v>
+        <v>5.87669515609741</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G592" t="n">
-        <v>5.94758319854736</v>
+        <v>5.94758367538452</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G593" t="n">
-        <v>5.89796209335327</v>
+        <v>5.89796161651611</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>5.9050498008728</v>
+        <v>5.90505027770996</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>5.91213989257812</v>
+        <v>5.91213798522949</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>5.99011707305908</v>
+        <v>5.99011659622192</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>6.06100654602051</v>
+        <v>6.06100702285767</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G603" t="n">
-        <v>6.19953012466431</v>
+        <v>6.19952964782715</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G606" t="n">
-        <v>6.09644985198975</v>
+        <v>6.0964503288269</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>5.97864484786987</v>
+        <v>5.97864437103271</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G608" t="n">
-        <v>6.08908748626709</v>
+        <v>6.08908796310425</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G609" t="n">
-        <v>6.08172464370728</v>
+        <v>6.08172512054443</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G611" t="n">
-        <v>6.08908748626709</v>
+        <v>6.08908796310425</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G613" t="n">
-        <v>5.97128057479858</v>
+        <v>5.97128105163574</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>5.87556409835815</v>
+        <v>5.87556505203247</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>8.25</v>
       </c>
       <c r="G616" t="n">
-        <v>6.07436227798462</v>
+        <v>6.07436180114746</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.25</v>
       </c>
       <c r="G617" t="n">
-        <v>6.07436227798462</v>
+        <v>6.07436180114746</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G618" t="n">
-        <v>6.0449104309082</v>
+        <v>6.04490995407104</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G619" t="n">
-        <v>6.08172464370728</v>
+        <v>6.08172512054443</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G621" t="n">
-        <v>6.08908748626709</v>
+        <v>6.08908796310425</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G622" t="n">
-        <v>6.11117553710938</v>
+        <v>6.11117696762085</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>6.19953012466431</v>
+        <v>6.19952964782715</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G624" t="n">
-        <v>6.18480491638184</v>
+        <v>6.18480443954468</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>6.00809621810913</v>
+        <v>6.00809574127197</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>5.98600721359253</v>
+        <v>5.98600769042969</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G630" t="n">
-        <v>6.02282190322876</v>
+        <v>6.0228214263916</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.00809621810913</v>
+        <v>6.00809574127197</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G633" t="n">
-        <v>6.02282190322876</v>
+        <v>6.0228214263916</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G634" t="n">
-        <v>5.97128057479858</v>
+        <v>5.97128105163574</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G635" t="n">
-        <v>5.87556409835815</v>
+        <v>5.87556505203247</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G637" t="n">
-        <v>5.87556409835815</v>
+        <v>5.87556505203247</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G638" t="n">
-        <v>5.86820077896118</v>
+        <v>5.86820125579834</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>5.83138751983643</v>
+        <v>5.83138704299927</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G640" t="n">
-        <v>5.80929851531982</v>
+        <v>5.80929899215698</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G641" t="n">
-        <v>5.94182968139648</v>
+        <v>5.94183015823364</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G642" t="n">
-        <v>5.95655536651611</v>
+        <v>5.95655632019043</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G644" t="n">
-        <v>5.91237831115723</v>
+        <v>5.91237878799438</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G646" t="n">
-        <v>5.90501642227173</v>
+        <v>5.90501594543457</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G648" t="n">
-        <v>5.9271035194397</v>
+        <v>5.92710447311401</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G650" t="n">
-        <v>5.95655536651611</v>
+        <v>5.95655632019043</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G651" t="n">
-        <v>5.95655536651611</v>
+        <v>5.95655632019043</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G652" t="n">
-        <v>5.88292694091797</v>
+        <v>5.88292741775513</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G653" t="n">
-        <v>5.82402467727661</v>
+        <v>5.82402420043945</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>5.77984666824341</v>
+        <v>5.77984714508057</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>5.83138751983643</v>
+        <v>5.83138704299927</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G657" t="n">
-        <v>5.97864484786987</v>
+        <v>5.97864437103271</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G658" t="n">
-        <v>5.97128057479858</v>
+        <v>5.97128105163574</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>5.98600721359253</v>
+        <v>5.98600769042969</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G660" t="n">
-        <v>5.97864484786987</v>
+        <v>5.97864437103271</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G662" t="n">
-        <v>5.98600721359253</v>
+        <v>5.98600769042969</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G663" t="n">
-        <v>5.9271035194397</v>
+        <v>5.92710447311401</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G664" t="n">
-        <v>5.91237831115723</v>
+        <v>5.91237878799438</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>5.91237831115723</v>
+        <v>5.91237878799438</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>5.74303340911865</v>
+        <v>5.74303293228149</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G668" t="n">
-        <v>5.77248477935791</v>
+        <v>5.77248430252075</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>7.75</v>
       </c>
       <c r="G670" t="n">
-        <v>5.70621871948242</v>
+        <v>5.70621824264526</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>5.86083889007568</v>
+        <v>5.86083841323853</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>5.84611320495605</v>
+        <v>5.8461127281189</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G675" t="n">
-        <v>5.84611320495605</v>
+        <v>5.8461127281189</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G676" t="n">
-        <v>5.88292694091797</v>
+        <v>5.88292741775513</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G678" t="n">
-        <v>5.87556409835815</v>
+        <v>5.87556505203247</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>5.74303340911865</v>
+        <v>5.74303293228149</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.8166618347168</v>
+        <v>5.81666135787964</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G684" t="n">
-        <v>5.69149255752563</v>
+        <v>5.69149351119995</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G685" t="n">
-        <v>5.8166618347168</v>
+        <v>5.81666135787964</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G686" t="n">
-        <v>5.91237831115723</v>
+        <v>5.91237878799438</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G687" t="n">
-        <v>5.86820077896118</v>
+        <v>5.86820125579834</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G688" t="n">
-        <v>5.8976526260376</v>
+        <v>5.89765310287476</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>8.25</v>
       </c>
       <c r="G689" t="n">
-        <v>6.07436227798462</v>
+        <v>6.07436180114746</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G690" t="n">
-        <v>6.05963563919067</v>
+        <v>6.05963611602783</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>6.28788423538208</v>
+        <v>6.28788471221924</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G693" t="n">
-        <v>6.27315950393677</v>
+        <v>6.27315998077393</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>6.3688759803772</v>
+        <v>6.36887645721436</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G697" t="n">
-        <v>6.3615140914917</v>
+        <v>6.36151361465454</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G699" t="n">
-        <v>6.45723056793213</v>
+        <v>6.45723152160645</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G700" t="n">
-        <v>6.34678745269775</v>
+        <v>6.3467869758606</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G702" t="n">
-        <v>6.3688759803772</v>
+        <v>6.36887645721436</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G704" t="n">
-        <v>6.4204158782959</v>
+        <v>6.42041635513306</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>6.40569067001343</v>
+        <v>6.40569019317627</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G707" t="n">
-        <v>6.15535306930542</v>
+        <v>6.15535259246826</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G709" t="n">
-        <v>6.22898197174072</v>
+        <v>6.22898149490356</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G710" t="n">
-        <v>6.08172464370728</v>
+        <v>6.08172512054443</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>6.28788423538208</v>
+        <v>6.28788471221924</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G713" t="n">
-        <v>6.33942413330078</v>
+        <v>6.33942461013794</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G714" t="n">
-        <v>6.39832782745361</v>
+        <v>6.39832735061646</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.35415077209473</v>
+        <v>6.35414981842041</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G716" t="n">
-        <v>6.37623882293701</v>
+        <v>6.37623929977417</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G719" t="n">
-        <v>6.08172464370728</v>
+        <v>6.08172512054443</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G720" t="n">
-        <v>6.16271591186523</v>
+        <v>6.16271543502808</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G721" t="n">
-        <v>6.03754758834839</v>
+        <v>6.03754663467407</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>6.22161817550659</v>
+        <v>6.22161865234375</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>6.19953012466431</v>
+        <v>6.19952964782715</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>6.0449104309082</v>
+        <v>6.04490995407104</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G725" t="n">
-        <v>6.15535306930542</v>
+        <v>6.15535259246826</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>6.14062738418579</v>
+        <v>6.14062833786011</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>6.22898197174072</v>
+        <v>6.22898149490356</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>6.10381269454956</v>
+        <v>6.10381364822388</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G729" t="n">
-        <v>6.28788423538208</v>
+        <v>6.28788471221924</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G730" t="n">
-        <v>6.4940447807312</v>
+        <v>6.49404430389404</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G731" t="n">
-        <v>6.3688759803772</v>
+        <v>6.36887645721436</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G733" t="n">
-        <v>6.54558515548706</v>
+        <v>6.54558420181274</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G734" t="n">
-        <v>6.55294752120972</v>
+        <v>6.55294799804688</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G735" t="n">
-        <v>6.55294752120972</v>
+        <v>6.55294799804688</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G736" t="n">
-        <v>6.45723056793213</v>
+        <v>6.45723152160645</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>6.35415077209473</v>
+        <v>6.35414981842041</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G740" t="n">
-        <v>6.10381269454956</v>
+        <v>6.10381364822388</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G741" t="n">
-        <v>6.16271591186523</v>
+        <v>6.16271543502808</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G742" t="n">
-        <v>6.17744207382202</v>
+        <v>6.17744255065918</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G743" t="n">
-        <v>6.09644985198975</v>
+        <v>6.0964503288269</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G744" t="n">
-        <v>6.3615140914917</v>
+        <v>6.36151361465454</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G745" t="n">
-        <v>6.28052139282227</v>
+        <v>6.28052186965942</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G746" t="n">
-        <v>6.11117553710938</v>
+        <v>6.11117696762085</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>6.28788423538208</v>
+        <v>6.28788471221924</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>6.22898197174072</v>
+        <v>6.22898149490356</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G750" t="n">
-        <v>6.18480491638184</v>
+        <v>6.18480443954468</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G751" t="n">
-        <v>6.14062738418579</v>
+        <v>6.14062833786011</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G752" t="n">
-        <v>6.14062738418579</v>
+        <v>6.14062833786011</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G754" t="n">
-        <v>6.17007923126221</v>
+        <v>6.17007875442505</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G755" t="n">
-        <v>6.17744207382202</v>
+        <v>6.17744255065918</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G756" t="n">
-        <v>6.17744207382202</v>
+        <v>6.17744255065918</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G757" t="n">
-        <v>6.01545858383179</v>
+        <v>6.01545810699463</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>6.03754758834839</v>
+        <v>6.03754663467407</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G759" t="n">
-        <v>6.18480491638184</v>
+        <v>6.18480443954468</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>6.10381269454956</v>
+        <v>6.10381364822388</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G762" t="n">
-        <v>6.05963563919067</v>
+        <v>6.05963611602783</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G764" t="n">
-        <v>6.21425628662109</v>
+        <v>6.21425580978394</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G769" t="n">
-        <v>6.56031036376953</v>
+        <v>6.56031084060669</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>6.58976125717163</v>
+        <v>6.58976173400879</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G772" t="n">
-        <v>6.53822231292725</v>
+        <v>6.53822135925293</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G773" t="n">
-        <v>6.6486644744873</v>
+        <v>6.64866542816162</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>6.66339159011841</v>
+        <v>6.66339063644409</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G776" t="n">
-        <v>6.6486644744873</v>
+        <v>6.64866542816162</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G777" t="n">
-        <v>6.56031036376953</v>
+        <v>6.56031084060669</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G779" t="n">
-        <v>6.64130258560181</v>
+        <v>6.64130306243896</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G781" t="n">
-        <v>6.70020484924316</v>
+        <v>6.70020532608032</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G782" t="n">
-        <v>6.78855991363525</v>
+        <v>6.7885594367981</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G783" t="n">
-        <v>6.78855991363525</v>
+        <v>6.7885594367981</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>6.69284296035767</v>
+        <v>6.69284248352051</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G787" t="n">
-        <v>6.84746265411377</v>
+        <v>6.84746217727661</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G788" t="n">
-        <v>6.89900159835815</v>
+        <v>6.89900302886963</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G789" t="n">
-        <v>6.94317960739136</v>
+        <v>6.9431791305542</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.25</v>
       </c>
       <c r="G791" t="n">
-        <v>6.8106484413147</v>
+        <v>6.81064748764038</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G792" t="n">
-        <v>6.87691307067871</v>
+        <v>6.87691450119019</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G794" t="n">
-        <v>6.88427639007568</v>
+        <v>6.88427686691284</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>9.75</v>
       </c>
       <c r="G795" t="n">
-        <v>7.17879056930542</v>
+        <v>7.17879199981689</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>7.14197731018066</v>
+        <v>7.14197826385498</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G797" t="n">
-        <v>7.12725210189819</v>
+        <v>7.12725067138672</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G798" t="n">
-        <v>6.91372776031494</v>
+        <v>6.9137282371521</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G799" t="n">
-        <v>6.94317960739136</v>
+        <v>6.9431791305542</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G800" t="n">
-        <v>6.92845296859741</v>
+        <v>6.92845344543457</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G801" t="n">
-        <v>6.92109060287476</v>
+        <v>6.92109107971191</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G802" t="n">
-        <v>7.03889751434326</v>
+        <v>7.03889656066895</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>9.5</v>
       </c>
       <c r="G804" t="n">
-        <v>6.9947190284729</v>
+        <v>6.99471950531006</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G805" t="n">
-        <v>6.98735618591309</v>
+        <v>6.98735666275024</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G806" t="n">
-        <v>6.98735618591309</v>
+        <v>6.98735666275024</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G807" t="n">
-        <v>6.95790433883667</v>
+        <v>6.95790576934814</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G808" t="n">
-        <v>7.12725210189819</v>
+        <v>7.12725067138672</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G809" t="n">
-        <v>7.16406536102295</v>
+        <v>7.16406440734863</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G810" t="n">
-        <v>7.21560621261597</v>
+        <v>7.21560573577881</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>7.21560621261597</v>
+        <v>7.21560573577881</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G812" t="n">
-        <v>7.21560621261597</v>
+        <v>7.21560573577881</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G813" t="n">
-        <v>7.27450942993164</v>
+        <v>7.27450799942017</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G816" t="n">
-        <v>7.52484560012817</v>
+        <v>7.52484655380249</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G817" t="n">
-        <v>7.52484560012817</v>
+        <v>7.52484655380249</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G818" t="n">
-        <v>7.56902313232422</v>
+        <v>7.5690221786499</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G819" t="n">
-        <v>7.42176628112793</v>
+        <v>7.42176675796509</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G820" t="n">
-        <v>7.46594285964966</v>
+        <v>7.46594429016113</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G821" t="n">
-        <v>7.35549926757812</v>
+        <v>7.35550022125244</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>7.29659700393677</v>
+        <v>7.29659748077393</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G824" t="n">
-        <v>7.37758874893188</v>
+        <v>7.37759017944336</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G825" t="n">
-        <v>7.28923320770264</v>
+        <v>7.28923463821411</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G826" t="n">
-        <v>7.34077262878418</v>
+        <v>7.34077453613281</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G827" t="n">
-        <v>7.37758874893188</v>
+        <v>7.37759017944336</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G828" t="n">
-        <v>7.46594285964966</v>
+        <v>7.46594429016113</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G831" t="n">
-        <v>7.25978231430054</v>
+        <v>7.25978136062622</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G832" t="n">
-        <v>7.37758874893188</v>
+        <v>7.37759017944336</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G834" t="n">
-        <v>7.25242042541504</v>
+        <v>7.25241994857788</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G835" t="n">
-        <v>7.25242042541504</v>
+        <v>7.25241994857788</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G836" t="n">
-        <v>7.23033046722412</v>
+        <v>7.23033094406128</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G837" t="n">
-        <v>7.25978231430054</v>
+        <v>7.25978136062622</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G838" t="n">
-        <v>7.25978231430054</v>
+        <v>7.25978136062622</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G840" t="n">
-        <v>7.48066902160645</v>
+        <v>7.48066854476929</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G841" t="n">
-        <v>7.67210292816162</v>
+        <v>7.67210340499878</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>7.65737724304199</v>
+        <v>7.65737628936768</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G843" t="n">
-        <v>7.65737724304199</v>
+        <v>7.65737628936768</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>7.65737724304199</v>
+        <v>7.65737628936768</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G845" t="n">
-        <v>8.0107946395874</v>
+        <v>8.01079368591309</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G846" t="n">
-        <v>8.36421203613281</v>
+        <v>8.3642110824585</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G847" t="n">
-        <v>8.24640560150146</v>
+        <v>8.24640655517578</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>8.24640560150146</v>
+        <v>8.24640655517578</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G849" t="n">
-        <v>7.93716526031494</v>
+        <v>7.9371657371521</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>8.17277717590332</v>
+        <v>8.17277908325195</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>8.17277717590332</v>
+        <v>8.17277908325195</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>8.17277717590332</v>
+        <v>8.17277908325195</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G853" t="n">
-        <v>8.24640560150146</v>
+        <v>8.24640655517578</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G854" t="n">
-        <v>7.8812518119812</v>
+        <v>7.88125085830688</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G855" t="n">
-        <v>7.85082197189331</v>
+        <v>7.85082292556763</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G858" t="n">
-        <v>7.80517816543579</v>
+        <v>7.80517911911011</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G861" t="n">
-        <v>7.85082197189331</v>
+        <v>7.85082292556763</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G864" t="n">
-        <v>7.63781642913818</v>
+        <v>7.63781547546387</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G865" t="n">
-        <v>7.63781642913818</v>
+        <v>7.63781547546387</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G866" t="n">
-        <v>7.50849008560181</v>
+        <v>7.50849103927612</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G867" t="n">
-        <v>7.63781642913818</v>
+        <v>7.63781547546387</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G871" t="n">
-        <v>7.85082197189331</v>
+        <v>7.85082292556763</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G872" t="n">
-        <v>7.6834602355957</v>
+        <v>7.68345928192139</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G874" t="n">
-        <v>7.83560800552368</v>
+        <v>7.83560705184937</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G880" t="n">
-        <v>7.62260103225708</v>
+        <v>7.62260246276855</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G882" t="n">
-        <v>7.80517816543579</v>
+        <v>7.80517911911011</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>11</v>
       </c>
       <c r="G885" t="n">
-        <v>8.36812591552734</v>
+        <v>8.36812400817871</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>8.06383037567139</v>
+        <v>8.06382942199707</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G888" t="n">
-        <v>8.09425926208496</v>
+        <v>8.09426021575928</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G889" t="n">
-        <v>7.85082197189331</v>
+        <v>7.85082292556763</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G890" t="n">
-        <v>8.06383037567139</v>
+        <v>8.06382942199707</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G891" t="n">
-        <v>7.97254085540771</v>
+        <v>7.97253942489624</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>7.91168165206909</v>
+        <v>7.91168069839478</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G898" t="n">
-        <v>7.91168165206909</v>
+        <v>7.91168069839478</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G900" t="n">
-        <v>7.83560800552368</v>
+        <v>7.83560705184937</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G901" t="n">
-        <v>7.85082197189331</v>
+        <v>7.85082292556763</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G902" t="n">
-        <v>7.8812518119812</v>
+        <v>7.88125085830688</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>7.91168165206909</v>
+        <v>7.91168069839478</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>7.91168165206909</v>
+        <v>7.91168069839478</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G912" t="n">
-        <v>7.85082197189331</v>
+        <v>7.85082292556763</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>7.7595329284668</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80517816543579</v>
+        <v>7.80517911911011</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G916" t="n">
-        <v>7.80517816543579</v>
+        <v>7.80517911911011</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G918" t="n">
-        <v>7.95732593536377</v>
+        <v>7.95732545852661</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G919" t="n">
-        <v>7.7595329284668</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G923" t="n">
-        <v>7.62260103225708</v>
+        <v>7.62260246276855</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G924" t="n">
-        <v>7.53131151199341</v>
+        <v>7.53131294250488</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G925" t="n">
-        <v>7.66824531555176</v>
+        <v>7.66824626922607</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G926" t="n">
-        <v>7.62260103225708</v>
+        <v>7.62260246276855</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G927" t="n">
-        <v>7.599778175354</v>
+        <v>7.59977912902832</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G930" t="n">
-        <v>7.63781642913818</v>
+        <v>7.63781547546387</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G933" t="n">
-        <v>7.58456230163574</v>
+        <v>7.58456420898438</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>7.45523881912231</v>
+        <v>7.45523834228516</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>7.83560800552368</v>
+        <v>7.83560705184937</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>7.83560800552368</v>
+        <v>7.83560705184937</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G940" t="n">
-        <v>8.06383037567139</v>
+        <v>8.06382942199707</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G941" t="n">
-        <v>7.97254085540771</v>
+        <v>7.97253942489624</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>8.06383037567139</v>
+        <v>8.06382942199707</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G943" t="n">
-        <v>8.17033195495605</v>
+        <v>8.17033290863037</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G944" t="n">
-        <v>8.09425926208496</v>
+        <v>8.09426021575928</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>8.06383037567139</v>
+        <v>8.06382942199707</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>7.91168165206909</v>
+        <v>7.91168069839478</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G949" t="n">
-        <v>7.63781642913818</v>
+        <v>7.63781547546387</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G952" t="n">
-        <v>7.599778175354</v>
+        <v>7.59977912902832</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G953" t="n">
-        <v>7.7595329284668</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>7.6834602355957</v>
+        <v>7.68345928192139</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>7.57695722579956</v>
+        <v>7.57695627212524</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>7.46284627914429</v>
+        <v>7.46284580230713</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G957" t="n">
-        <v>7.5160984992981</v>
+        <v>7.51609706878662</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G958" t="n">
-        <v>7.77474880218506</v>
+        <v>7.77474927902222</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G960" t="n">
-        <v>7.66824531555176</v>
+        <v>7.66824626922607</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G961" t="n">
-        <v>7.71389007568359</v>
+        <v>7.71389102935791</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G962" t="n">
-        <v>7.66824531555176</v>
+        <v>7.66824626922607</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G965" t="n">
-        <v>7.49327564239502</v>
+        <v>7.49327516555786</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G966" t="n">
-        <v>7.53131151199341</v>
+        <v>7.53131294250488</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G967" t="n">
-        <v>7.50849008560181</v>
+        <v>7.50849103927612</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G968" t="n">
-        <v>7.53131151199341</v>
+        <v>7.53131294250488</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>7.7595329284668</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G970" t="n">
-        <v>7.63781642913818</v>
+        <v>7.63781547546387</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>7.6834602355957</v>
+        <v>7.68345928192139</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G972" t="n">
-        <v>7.6834602355957</v>
+        <v>7.68345928192139</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>7.6834602355957</v>
+        <v>7.68345928192139</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>7.6834602355957</v>
+        <v>7.68345928192139</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G975" t="n">
-        <v>7.85082197189331</v>
+        <v>7.85082292556763</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>7.7595329284668</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>7.7595329284668</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G978" t="n">
-        <v>7.77474880218506</v>
+        <v>7.77474927902222</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G983" t="n">
-        <v>8.56591510772705</v>
+        <v>8.56591701507568</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G984" t="n">
-        <v>9.09843444824219</v>
+        <v>9.09843349456787</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>9.20493698120117</v>
+        <v>9.20493602752686</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>12.5</v>
       </c>
       <c r="G987" t="n">
-        <v>9.50923156738281</v>
+        <v>9.50923347473145</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G988" t="n">
-        <v>9.64616584777832</v>
+        <v>9.64616775512695</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G990" t="n">
-        <v>9.64616584777832</v>
+        <v>9.64616775512695</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G992" t="n">
-        <v>9.7070255279541</v>
+        <v>9.70702457427979</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G998" t="n">
-        <v>9.87438488006592</v>
+        <v>9.87438678741455</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G999" t="n">
-        <v>9.64616584777832</v>
+        <v>9.64616775512695</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.7070255279541</v>
+        <v>9.70702457427979</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.61573696136475</v>
+        <v>9.61573505401611</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.60052013397217</v>
+        <v>9.60052108764648</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>12.5</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.50923156738281</v>
+        <v>9.50923347473145</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1011" t="n">
-        <v>9.29622650146484</v>
+        <v>9.29622554779053</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.61573696136475</v>
+        <v>9.61573505401611</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.64616584777832</v>
+        <v>9.64616775512695</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.67659664154053</v>
+        <v>9.67659568786621</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>12.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.50923156738281</v>
+        <v>9.50923347473145</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>12.5</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.50923156738281</v>
+        <v>9.50923347473145</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1021" t="n">
-        <v>9.7070255279541</v>
+        <v>9.70702457427979</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.73745536804199</v>
+        <v>9.73745632171631</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1026" t="n">
-        <v>9.82874202728271</v>
+        <v>9.82874298095703</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1027" t="n">
-        <v>10.0569639205933</v>
+        <v>10.0569648742676</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>10.0113201141357</v>
+        <v>10.0113191604614</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1030" t="n">
-        <v>10.133038520813</v>
+        <v>10.1330375671387</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>10.3156156539917</v>
+        <v>10.3156147003174</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1033" t="n">
-        <v>10.3003997802734</v>
+        <v>10.3004007339478</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1034" t="n">
-        <v>10.3156156539917</v>
+        <v>10.3156147003174</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1035" t="n">
-        <v>10.3003997802734</v>
+        <v>10.3004007339478</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1036" t="n">
-        <v>10.2851858139038</v>
+        <v>10.2851867675781</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>13.5</v>
       </c>
       <c r="G1037" t="n">
-        <v>10.2699718475342</v>
+        <v>10.2699708938599</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1038" t="n">
-        <v>10.3156156539917</v>
+        <v>10.3156147003174</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1039" t="n">
-        <v>10.3308305740356</v>
+        <v>10.3308296203613</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1040" t="n">
-        <v>10.4373340606689</v>
+        <v>10.4373331069946</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1041" t="n">
-        <v>10.6655559539795</v>
+        <v>10.6655550003052</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>10.635124206543</v>
+        <v>10.6351251602173</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>10.8024883270264</v>
+        <v>10.8024873733521</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1045" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089918136597</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1046" t="n">
-        <v>10.8329181671143</v>
+        <v>10.8329172134399</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1048" t="n">
-        <v>10.8481311798096</v>
+        <v>10.8481321334839</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1049" t="n">
-        <v>10.7872734069824</v>
+        <v>10.7872724533081</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1050" t="n">
-        <v>10.7568435668945</v>
+        <v>10.7568445205688</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>14</v>
       </c>
       <c r="G1051" t="n">
-        <v>10.6503410339355</v>
+        <v>10.6503400802612</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1052" t="n">
-        <v>10.4829778671265</v>
+        <v>10.4829769134521</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1053" t="n">
-        <v>9.76788520812988</v>
+        <v>9.76788425445557</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1054" t="n">
-        <v>9.82874202728271</v>
+        <v>9.82874298095703</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.26579570770264</v>
+        <v>9.26579761505127</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1062" t="n">
-        <v>8.71806526184082</v>
+        <v>8.7180643081665</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1066" t="n">
-        <v>7.10529804229736</v>
+        <v>7.10529947280884</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1068" t="n">
-        <v>7.28787612915039</v>
+        <v>7.28787660598755</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1070" t="n">
-        <v>7.31830549240112</v>
+        <v>7.31830501556396</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.6834602355957</v>
+        <v>7.68345928192139</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.2726616859436</v>
+        <v>7.27266073226929</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G1073" t="n">
-        <v>7.50849008560181</v>
+        <v>7.50849103927612</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1075" t="n">
-        <v>7.62260103225708</v>
+        <v>7.62260246276855</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1076" t="n">
-        <v>8.41377067565918</v>
+        <v>8.41376972198486</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1081" t="n">
-        <v>9.17450714111328</v>
+        <v>9.1745080947876</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1084" t="n">
-        <v>8.67242050170898</v>
+        <v>8.67241954803467</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1086" t="n">
-        <v>9.11364841461182</v>
+        <v>9.1136474609375</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1087" t="n">
-        <v>9.20493698120117</v>
+        <v>9.20493602752686</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.71806526184082</v>
+        <v>8.7180643081665</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.62677478790283</v>
+        <v>8.62677574157715</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1092" t="n">
-        <v>8.67242050170898</v>
+        <v>8.67241954803467</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1093" t="n">
-        <v>8.61156177520752</v>
+        <v>8.6115608215332</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1094" t="n">
-        <v>8.85499668121338</v>
+        <v>8.8549976348877</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.61156177520752</v>
+        <v>8.6115608215332</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1099" t="n">
-        <v>8.64199066162109</v>
+        <v>8.64198970794678</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1100" t="n">
-        <v>8.79413795471191</v>
+        <v>8.79413890838623</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1101" t="n">
-        <v>8.77892398834229</v>
+        <v>8.77892303466797</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>8.94628620147705</v>
+        <v>8.94628715515137</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1107" t="n">
-        <v>8.74663352966309</v>
+        <v>8.74663257598877</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.25720024108887</v>
+        <v>8.25719928741455</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1111" t="n">
-        <v>8.92030143737793</v>
+        <v>8.92030048370361</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1112" t="n">
-        <v>8.66769218444824</v>
+        <v>8.66769123077393</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.71505641937256</v>
+        <v>8.71505546569824</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1117" t="n">
-        <v>9.06239604949951</v>
+        <v>9.06239414215088</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1119" t="n">
-        <v>9.3307933807373</v>
+        <v>9.33079433441162</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1120" t="n">
-        <v>9.96231842041016</v>
+        <v>9.96231937408447</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1121" t="n">
-        <v>9.77286148071289</v>
+        <v>9.77286243438721</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1122" t="n">
-        <v>10.0096845626831</v>
+        <v>10.0096855163574</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1123" t="n">
-        <v>9.88337993621826</v>
+        <v>9.88337898254395</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1124" t="n">
-        <v>9.96231842041016</v>
+        <v>9.96231937408447</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1126" t="n">
-        <v>9.97810840606689</v>
+        <v>9.97810745239258</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234588623047</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.40973567962646</v>
+        <v>9.40973472595215</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1131" t="n">
-        <v>9.83601379394531</v>
+        <v>9.83601474761963</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1134" t="n">
-        <v>9.96231842041016</v>
+        <v>9.96231937408447</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1137" t="n">
-        <v>9.88337993621826</v>
+        <v>9.88337898254395</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.2465047836304</v>
+        <v>10.246506690979</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1139" t="n">
-        <v>10.5306930541992</v>
+        <v>10.5306921005249</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.5149049758911</v>
+        <v>10.5149040222168</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.0990657806396</v>
+        <v>11.099066734314</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.1306428909302</v>
+        <v>11.1306419372559</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.1464309692383</v>
+        <v>11.146430015564</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1162" t="n">
-        <v>10.8780326843262</v>
+        <v>10.8780317306519</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1164" t="n">
-        <v>10.5306930541992</v>
+        <v>10.5306921005249</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1169" t="n">
-        <v>10.2149286270142</v>
+        <v>10.2149295806885</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1171" t="n">
-        <v>10.2149286270142</v>
+        <v>10.2149295806885</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1174" t="n">
-        <v>10.2938709259033</v>
+        <v>10.293869972229</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1175" t="n">
-        <v>10.4201765060425</v>
+        <v>10.4201755523682</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.3096580505371</v>
+        <v>10.3096590042114</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.1991415023804</v>
+        <v>10.1991424560547</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.2780828475952</v>
+        <v>10.2780838012695</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1182" t="n">
-        <v>10.2149286270142</v>
+        <v>10.2149295806885</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>13</v>
       </c>
       <c r="G1186" t="n">
-        <v>10.2622938156128</v>
+        <v>10.2622947692871</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>13</v>
       </c>
       <c r="G1187" t="n">
-        <v>10.2622938156128</v>
+        <v>10.2622947692871</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1188" t="n">
-        <v>10.1044139862061</v>
+        <v>10.1044130325317</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1189" t="n">
-        <v>10.1044139862061</v>
+        <v>10.1044130325317</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1191" t="n">
-        <v>10.3096580505371</v>
+        <v>10.3096590042114</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1192" t="n">
-        <v>10.4201765060425</v>
+        <v>10.4201755523682</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1193" t="n">
-        <v>10.4201765060425</v>
+        <v>10.4201755523682</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>10.7359380722046</v>
+        <v>10.7359371185303</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1197" t="n">
-        <v>10.6727867126465</v>
+        <v>10.6727876663208</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1198" t="n">
-        <v>10.7359380722046</v>
+        <v>10.7359371185303</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1202" t="n">
-        <v>10.3570232391357</v>
+        <v>10.3570222854614</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1218" t="n">
-        <v>10.6727867126465</v>
+        <v>10.6727876663208</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1224" t="n">
-        <v>10.7359380722046</v>
+        <v>10.7359371185303</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1227" t="n">
-        <v>9.69392108917236</v>
+        <v>9.69392013549805</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1230" t="n">
-        <v>9.83601379394531</v>
+        <v>9.83601474761963</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1232" t="n">
-        <v>10.1359901428223</v>
+        <v>10.1359891891479</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1233" t="n">
-        <v>10.1991415023804</v>
+        <v>10.1991424560547</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1235" t="n">
-        <v>10.4201765060425</v>
+        <v>10.4201755523682</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1236" t="n">
-        <v>10.2149286270142</v>
+        <v>10.2149295806885</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1237" t="n">
-        <v>10.1991415023804</v>
+        <v>10.1991424560547</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1239" t="n">
-        <v>10.2938709259033</v>
+        <v>10.293869972229</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1242" t="n">
-        <v>10.8306684494019</v>
+        <v>10.8306674957275</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1246" t="n">
-        <v>10.5149049758911</v>
+        <v>10.5149040222168</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1254" t="n">
-        <v>10.6727867126465</v>
+        <v>10.6727876663208</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1257" t="n">
-        <v>10.4201765060425</v>
+        <v>10.4201755523682</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1260" t="n">
-        <v>10.4201765060425</v>
+        <v>10.4201755523682</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1261" t="n">
-        <v>10.2938709259033</v>
+        <v>10.293869972229</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.3570232391357</v>
+        <v>10.3570222854614</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1268" t="n">
-        <v>10.9253959655762</v>
+        <v>10.9253950119019</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1271" t="n">
-        <v>10.8780326843262</v>
+        <v>10.8780317306519</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1275" t="n">
-        <v>10.5306930541992</v>
+        <v>10.5306921005249</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1279" t="n">
-        <v>10.8780326843262</v>
+        <v>10.8780317306519</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1280" t="n">
-        <v>11.0201253890991</v>
+        <v>11.0201244354248</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1281" t="n">
-        <v>11.0674905776978</v>
+        <v>11.0674896240234</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1282" t="n">
-        <v>11.0674905776978</v>
+        <v>11.0674896240234</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1283" t="n">
-        <v>11.0990657806396</v>
+        <v>11.099066734314</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1285" t="n">
-        <v>10.8780326843262</v>
+        <v>10.8780317306519</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>10.7359380722046</v>
+        <v>10.7359371185303</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G1287" t="n">
-        <v>10.8464555740356</v>
+        <v>10.84645652771</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1288" t="n">
-        <v>10.6885738372803</v>
+        <v>10.6885747909546</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1289" t="n">
-        <v>10.6727867126465</v>
+        <v>10.6727876663208</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.6727867126465</v>
+        <v>10.6727876663208</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1297" t="n">
-        <v>11.3674640655518</v>
+        <v>11.3674631118774</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>11.3674640655518</v>
+        <v>11.3674631118774</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1300" t="n">
-        <v>11.6674385070801</v>
+        <v>11.6674394607544</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.9516267776489</v>
+        <v>11.9516258239746</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>15</v>
       </c>
       <c r="G1303" t="n">
-        <v>11.8411092758179</v>
+        <v>11.8411083221436</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1306" t="n">
-        <v>11.462194442749</v>
+        <v>11.4621934890747</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.2569465637207</v>
+        <v>11.2569484710693</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.604287147522</v>
+        <v>11.6042852401733</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.6358623504639</v>
+        <v>11.6358633041382</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1313" t="n">
-        <v>11.6674385070801</v>
+        <v>11.6674394607544</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1315" t="n">
-        <v>11.8253202438354</v>
+        <v>11.8253211975098</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>15</v>
       </c>
       <c r="G1316" t="n">
-        <v>11.8411092758179</v>
+        <v>11.8411083221436</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>11.9200496673584</v>
+        <v>11.9200506210327</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1320" t="n">
-        <v>12.1410827636719</v>
+        <v>12.1410837173462</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>12.7883987426758</v>
+        <v>12.7883968353271</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1336" t="n">
-        <v>13.3251943588257</v>
+        <v>13.3251934051514</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1337" t="n">
-        <v>13.3251943588257</v>
+        <v>13.3251934051514</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>17</v>
       </c>
       <c r="G1338" t="n">
-        <v>13.4199237823486</v>
+        <v>13.419921875</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1339" t="n">
-        <v>13.6409587860107</v>
+        <v>13.6409578323364</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1341" t="n">
-        <v>13.8462038040161</v>
+        <v>13.8462047576904</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1346" t="n">
-        <v>13.4041337966919</v>
+        <v>13.4041357040405</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1348" t="n">
-        <v>13.2462539672852</v>
+        <v>13.2462549209595</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1349" t="n">
-        <v>13.4357118606567</v>
+        <v>13.4357128143311</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>17</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.4199237823486</v>
+        <v>13.419921875</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1352" t="n">
-        <v>13.5935916900635</v>
+        <v>13.5935935974121</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1355" t="n">
-        <v>13.7356863021851</v>
+        <v>13.7356853485107</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1356" t="n">
-        <v>13.8304147720337</v>
+        <v>13.8304138183594</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1358" t="n">
-        <v>14.0514488220215</v>
+        <v>14.0514497756958</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1359" t="n">
-        <v>14.1320199966431</v>
+        <v>14.1320209503174</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1360" t="n">
-        <v>13.7775106430054</v>
+        <v>13.7775096893311</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1361" t="n">
-        <v>13.7452821731567</v>
+        <v>13.7452812194824</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1364" t="n">
-        <v>13.874192237854</v>
+        <v>13.8741941452026</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>17</v>
       </c>
       <c r="G1366" t="n">
-        <v>13.6969404220581</v>
+        <v>13.6969385147095</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1371" t="n">
-        <v>13.5841417312622</v>
+        <v>13.5841426849365</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1372" t="n">
-        <v>13.406886100769</v>
+        <v>13.4068870544434</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1374" t="n">
-        <v>13.6485986709595</v>
+        <v>13.6485977172852</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1375" t="n">
-        <v>13.6002559661865</v>
+        <v>13.6002550125122</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1376" t="n">
-        <v>13.5680274963379</v>
+        <v>13.5680265426636</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1377" t="n">
-        <v>13.6485986709595</v>
+        <v>13.6485977172852</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1378" t="n">
-        <v>13.6324844360352</v>
+        <v>13.6324834823608</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1379" t="n">
-        <v>13.7775106430054</v>
+        <v>13.7775096893311</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1380" t="n">
-        <v>13.9064235687256</v>
+        <v>13.906421661377</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1384" t="n">
-        <v>13.9225378036499</v>
+        <v>13.9225368499756</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1386" t="n">
-        <v>13.7452821731567</v>
+        <v>13.7452812194824</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1387" t="n">
-        <v>13.6324844360352</v>
+        <v>13.6324834823608</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1389" t="n">
-        <v>13.6324844360352</v>
+        <v>13.6324834823608</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>13.5357980728149</v>
+        <v>13.5357990264893</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>17</v>
       </c>
       <c r="G1392" t="n">
-        <v>13.6969404220581</v>
+        <v>13.6969385147095</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1393" t="n">
-        <v>13.5519132614136</v>
+        <v>13.5519123077393</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1394" t="n">
-        <v>13.5841417312622</v>
+        <v>13.5841426849365</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1396" t="n">
-        <v>13.5357980728149</v>
+        <v>13.5357990264893</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>13.9386491775513</v>
+        <v>13.9386510848999</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1408" t="n">
-        <v>13.7452821731567</v>
+        <v>13.7452812194824</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>13.7452821731567</v>
+        <v>13.7452812194824</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1412" t="n">
-        <v>13.7775106430054</v>
+        <v>13.7775096893311</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>13.5841417312622</v>
+        <v>13.5841426849365</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1418" t="n">
-        <v>13.7775106430054</v>
+        <v>13.7775096893311</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>14.3415012359619</v>
+        <v>14.3415021896362</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1423" t="n">
-        <v>14.2609310150146</v>
+        <v>14.2609329223633</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1424" t="n">
-        <v>14.3415012359619</v>
+        <v>14.3415021896362</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1427" t="n">
-        <v>14.6637830734253</v>
+        <v>14.6637840270996</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1428" t="n">
-        <v>14.8732652664185</v>
+        <v>14.8732633590698</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1429" t="n">
-        <v>14.8732652664185</v>
+        <v>14.8732633590698</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1430" t="n">
-        <v>14.6637830734253</v>
+        <v>14.6637840270996</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1434" t="n">
-        <v>14.9216089248657</v>
+        <v>14.9216060638428</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1435" t="n">
-        <v>15.2438879013062</v>
+        <v>15.2438888549805</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1436" t="n">
-        <v>15.0827465057373</v>
+        <v>15.0827474594116</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1438" t="n">
-        <v>14.8410396575928</v>
+        <v>14.8410367965698</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1439" t="n">
-        <v>14.8249235153198</v>
+        <v>14.8249225616455</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1441" t="n">
-        <v>14.7765827178955</v>
+        <v>14.7765808105469</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1443" t="n">
-        <v>14.5509834289551</v>
+        <v>14.5509853363037</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1446" t="n">
-        <v>14.3898448944092</v>
+        <v>14.3898429870605</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>14.3415012359619</v>
+        <v>14.3415021896362</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1448" t="n">
-        <v>14.3576145172119</v>
+        <v>14.3576164245605</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>14.3576145172119</v>
+        <v>14.3576164245605</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1451" t="n">
-        <v>14.8410396575928</v>
+        <v>14.8410367965698</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1452" t="n">
-        <v>14.6960115432739</v>
+        <v>14.6960096359253</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1455" t="n">
-        <v>14.3415012359619</v>
+        <v>14.3415021896362</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1456" t="n">
-        <v>14.3576145172119</v>
+        <v>14.3576164245605</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1457" t="n">
-        <v>14.5348720550537</v>
+        <v>14.534873008728</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1458" t="n">
-        <v>14.4381856918335</v>
+        <v>14.4381866455078</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1459" t="n">
-        <v>14.3737297058105</v>
+        <v>14.3737287521362</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1461" t="n">
-        <v>13.9386491775513</v>
+        <v>13.9386510848999</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1465" t="n">
-        <v>13.6485986709595</v>
+        <v>13.6485977172852</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1467" t="n">
-        <v>13.6324844360352</v>
+        <v>13.6324834823608</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1468" t="n">
-        <v>13.6002559661865</v>
+        <v>13.6002550125122</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>16.5</v>
       </c>
       <c r="G1469" t="n">
-        <v>13.2940902709961</v>
+        <v>13.2940883636475</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1470" t="n">
-        <v>13.3102025985718</v>
+        <v>13.3102035522461</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1472" t="n">
-        <v>14.0192213058472</v>
+        <v>14.0192203521729</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1473" t="n">
-        <v>14.1320199966431</v>
+        <v>14.1320209503174</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1476" t="n">
-        <v>14.0514478683472</v>
+        <v>14.0514488220215</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1477" t="n">
-        <v>14.1481323242188</v>
+        <v>14.1481332778931</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1478" t="n">
-        <v>14.1159048080444</v>
+        <v>14.1159038543701</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1479" t="n">
-        <v>14.0031051635742</v>
+        <v>14.0031061172485</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1480" t="n">
-        <v>14.1159048080444</v>
+        <v>14.1159038543701</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1481" t="n">
-        <v>14.1159048080444</v>
+        <v>14.1159038543701</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1482" t="n">
-        <v>14.1159048080444</v>
+        <v>14.1159038543701</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1483" t="n">
-        <v>14.0514478683472</v>
+        <v>14.0514488220215</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1485" t="n">
-        <v>13.9869937896729</v>
+        <v>13.9869928359985</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1486" t="n">
-        <v>13.9869937896729</v>
+        <v>13.9869928359985</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1487" t="n">
-        <v>13.9708795547485</v>
+        <v>13.9708786010742</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1488" t="n">
-        <v>14.5509834289551</v>
+        <v>14.5509853363037</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1489" t="n">
-        <v>15.01828956604</v>
+        <v>15.0182905197144</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1490" t="n">
-        <v>14.6637830734253</v>
+        <v>14.6637840270996</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1492" t="n">
-        <v>14.5348720550537</v>
+        <v>14.534873008728</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1493" t="n">
-        <v>14.5832138061523</v>
+        <v>14.5832118988037</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1495" t="n">
-        <v>14.4381856918335</v>
+        <v>14.4381866455078</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1496" t="n">
-        <v>14.0514478683472</v>
+        <v>14.0514488220215</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1497" t="n">
-        <v>14.0675611495972</v>
+        <v>14.0675630569458</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1498" t="n">
-        <v>13.9869937896729</v>
+        <v>13.9869928359985</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.6002559661865</v>
+        <v>13.6002550125122</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1504" t="n">
-        <v>13.5841417312622</v>
+        <v>13.5841426849365</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>17</v>
       </c>
       <c r="G1506" t="n">
-        <v>13.6969404220581</v>
+        <v>13.6969385147095</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1507" t="n">
-        <v>13.3746585845947</v>
+        <v>13.374659538269</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1508" t="n">
-        <v>13.2457475662231</v>
+        <v>13.2457466125488</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1509" t="n">
-        <v>13.3424291610718</v>
+        <v>13.3424301147461</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1510" t="n">
-        <v>13.9064235687256</v>
+        <v>13.906421661377</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1512" t="n">
-        <v>13.6485986709595</v>
+        <v>13.6485977172852</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1513" t="n">
-        <v>13.7775106430054</v>
+        <v>13.7775096893311</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>13.3746585845947</v>
+        <v>13.374659538269</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1517" t="n">
-        <v>13.3102025985718</v>
+        <v>13.3102035522461</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1518" t="n">
-        <v>13.020149230957</v>
+        <v>13.0201501846313</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="n">
-        <v>13.5357980728149</v>
+        <v>13.5357990264893</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1524" t="n">
-        <v>13.5841417312622</v>
+        <v>13.5841426849365</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1525" t="n">
-        <v>13.6002559661865</v>
+        <v>13.6002550125122</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1527" t="n">
-        <v>13.6485986709595</v>
+        <v>13.6485977172852</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1528" t="n">
-        <v>13.6324844360352</v>
+        <v>13.6324834823608</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1529" t="n">
-        <v>13.6002559661865</v>
+        <v>13.6002550125122</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1535" t="n">
-        <v>13.020149230957</v>
+        <v>13.0201501846313</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G1539" t="n">
-        <v>12.9234666824341</v>
+        <v>12.9234657287598</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1545" t="n">
-        <v>12.0694208145142</v>
+        <v>12.0694217681885</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1548" t="n">
-        <v>11.9727354049683</v>
+        <v>11.9727363586426</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1549" t="n">
-        <v>11.9888515472412</v>
+        <v>11.9888505935669</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1561" t="n">
-        <v>10.9897794723511</v>
+        <v>10.9897804260254</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1564" t="n">
-        <v>10.5224723815918</v>
+        <v>10.5224733352661</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1565" t="n">
-        <v>9.9101390838623</v>
+        <v>9.91013813018799</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1568" t="n">
-        <v>9.95847988128662</v>
+        <v>9.95848083496094</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1569" t="n">
-        <v>9.89402484893799</v>
+        <v>9.89402389526367</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1570" t="n">
-        <v>9.68454170227051</v>
+        <v>9.68454265594482</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>9.34614753723145</v>
+        <v>9.34614658355713</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1576" t="n">
-        <v>9.24946403503418</v>
+        <v>9.24946212768555</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1578" t="n">
-        <v>9.12055015563965</v>
+        <v>9.12055110931396</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1579" t="n">
-        <v>9.89402484893799</v>
+        <v>9.89402389526367</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1581" t="n">
-        <v>10.2968759536743</v>
+        <v>10.296875</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1583" t="n">
-        <v>10.1840782165527</v>
+        <v>10.1840772628784</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1586" t="n">
-        <v>9.84568309783936</v>
+        <v>9.84568214416504</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1588" t="n">
-        <v>9.89402484893799</v>
+        <v>9.89402389526367</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1593" t="n">
-        <v>9.33003234863281</v>
+        <v>9.33003330230713</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1594" t="n">
-        <v>8.9110689163208</v>
+        <v>8.91106700897217</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1596" t="n">
-        <v>9.10443592071533</v>
+        <v>9.10443496704102</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1598" t="n">
-        <v>9.02386569976807</v>
+        <v>9.02386665344238</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1600" t="n">
-        <v>8.9110689163208</v>
+        <v>8.91106700897217</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1602" t="n">
-        <v>9.15277862548828</v>
+        <v>9.15277767181396</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1607" t="n">
-        <v>9.15277862548828</v>
+        <v>9.15277767181396</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1608" t="n">
-        <v>9.24946403503418</v>
+        <v>9.24946212768555</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1610" t="n">
-        <v>9.73288440704346</v>
+        <v>9.73288536071777</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1611" t="n">
-        <v>10.2324199676514</v>
+        <v>10.2324190139771</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1614" t="n">
-        <v>9.63619995117188</v>
+        <v>9.63619899749756</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1616" t="n">
-        <v>9.41946887969971</v>
+        <v>9.41946792602539</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1618" t="n">
-        <v>9.41946887969971</v>
+        <v>9.41946792602539</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1619" t="n">
-        <v>9.76957321166992</v>
+        <v>9.76957225799561</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1622" t="n">
-        <v>9.56951427459717</v>
+        <v>9.56951332092285</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1627" t="n">
-        <v>10.3364086151123</v>
+        <v>10.336407661438</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1640" t="n">
-        <v>9.73622894287109</v>
+        <v>9.73622989654541</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1641" t="n">
-        <v>9.71955871582031</v>
+        <v>9.719557762146</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1643" t="n">
-        <v>9.76957321166992</v>
+        <v>9.76957225799561</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1645" t="n">
-        <v>9.73622894287109</v>
+        <v>9.73622989654541</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1648" t="n">
-        <v>9.76957321166992</v>
+        <v>9.76957225799561</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1662" t="n">
-        <v>9.73622894287109</v>
+        <v>9.73622989654541</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1664" t="n">
-        <v>9.56951427459717</v>
+        <v>9.56951332092285</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1665" t="n">
-        <v>9.73622894287109</v>
+        <v>9.73622989654541</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1668" t="n">
-        <v>9.86960315704346</v>
+        <v>9.86960220336914</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1674" t="n">
-        <v>10.3197364807129</v>
+        <v>10.3197374343872</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1675" t="n">
-        <v>10.1196765899658</v>
+        <v>10.1196775436401</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1683" t="n">
-        <v>10.3364086151123</v>
+        <v>10.336407661438</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1684" t="n">
-        <v>10.4364395141602</v>
+        <v>10.4364385604858</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1685" t="n">
-        <v>10.3697509765625</v>
+        <v>10.3697519302368</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1687" t="n">
-        <v>10.1863641738892</v>
+        <v>10.1863632202148</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1689" t="n">
-        <v>9.81958866119385</v>
+        <v>9.81958770751953</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1690" t="n">
-        <v>9.76957321166992</v>
+        <v>9.76957225799561</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1692" t="n">
-        <v>9.81958866119385</v>
+        <v>9.81958770751953</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1695" t="n">
-        <v>9.46948432922363</v>
+        <v>9.46948337554932</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1696" t="n">
-        <v>9.46948432922363</v>
+        <v>9.46948337554932</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1698" t="n">
-        <v>9.46948432922363</v>
+        <v>9.46948337554932</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1702" t="n">
-        <v>9.51949882507324</v>
+        <v>9.51949787139893</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1703" t="n">
-        <v>9.61952877044678</v>
+        <v>9.61952781677246</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1707" t="n">
-        <v>9.61952877044678</v>
+        <v>9.61952781677246</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1708" t="n">
-        <v>9.51949882507324</v>
+        <v>9.51949787139893</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1719" t="n">
-        <v>9.26942443847656</v>
+        <v>9.26942348480225</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1720" t="n">
-        <v>9.61952877044678</v>
+        <v>9.61952781677246</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1721" t="n">
-        <v>9.61952877044678</v>
+        <v>9.61952781677246</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1722" t="n">
-        <v>9.61952877044678</v>
+        <v>9.61952781677246</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1723" t="n">
-        <v>9.41946887969971</v>
+        <v>9.41946792602539</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1725" t="n">
-        <v>9.26942443847656</v>
+        <v>9.26942348480225</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1728" t="n">
-        <v>9.3694543838501</v>
+        <v>9.36945343017578</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G1733" t="n">
-        <v>10.2863941192627</v>
+        <v>10.2863931655884</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1741" t="n">
-        <v>10.4364395141602</v>
+        <v>10.4364385604858</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1742" t="n">
-        <v>10.4864530563354</v>
+        <v>10.4864521026611</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1746" t="n">
-        <v>11.7201528549194</v>
+        <v>11.7201538085938</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1754" t="n">
-        <v>11.5867805480957</v>
+        <v>11.5867795944214</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>14</v>
       </c>
       <c r="G1756" t="n">
-        <v>11.6701374053955</v>
+        <v>11.6701383590698</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>14</v>
       </c>
       <c r="G1757" t="n">
-        <v>11.6701374053955</v>
+        <v>11.6701383590698</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>14</v>
       </c>
       <c r="G1761" t="n">
-        <v>11.6701374053955</v>
+        <v>11.6701383590698</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>14</v>
       </c>
       <c r="G1775" t="n">
-        <v>11.6701374053955</v>
+        <v>11.6701383590698</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1776" t="n">
-        <v>11.770167350769</v>
+        <v>11.7701683044434</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1777" t="n">
-        <v>11.7201528549194</v>
+        <v>11.7201538085938</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1780" t="n">
-        <v>11.820182800293</v>
+        <v>11.8201837539673</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1785" t="n">
-        <v>12.2869873046875</v>
+        <v>12.2869882583618</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1786" t="n">
-        <v>12.2869873046875</v>
+        <v>12.2869882583618</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1787" t="n">
-        <v>12.5370626449585</v>
+        <v>12.5370635986328</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1788" t="n">
-        <v>12.687108039856</v>
+        <v>12.6871089935303</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1791" t="n">
-        <v>12.687108039856</v>
+        <v>12.6871089935303</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1802" t="n">
-        <v>13.1705856323242</v>
+        <v>13.1705846786499</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1807" t="n">
-        <v>13.2206001281738</v>
+        <v>13.2205991744995</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1814" t="n">
-        <v>14.187554359436</v>
+        <v>14.1875553131104</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1815" t="n">
-        <v>14.3042554855347</v>
+        <v>14.3042545318604</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1816" t="n">
-        <v>14.2208967208862</v>
+        <v>14.2208957672119</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1818" t="n">
-        <v>14.2542409896851</v>
+        <v>14.2542400360107</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1819" t="n">
-        <v>14.35426902771</v>
+        <v>14.3542699813843</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1821" t="n">
-        <v>14.5710020065308</v>
+        <v>14.5710010528564</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1822" t="n">
-        <v>14.6210165023804</v>
+        <v>14.621018409729</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1824" t="n">
-        <v>14.7543897628784</v>
+        <v>14.7543916702271</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1825" t="n">
-        <v>14.6210165023804</v>
+        <v>14.621018409729</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1835" t="n">
-        <v>13.9708232879639</v>
+        <v>13.9708223342896</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1836" t="n">
-        <v>14.5209875106812</v>
+        <v>14.5209865570068</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1838" t="n">
-        <v>14.6210165023804</v>
+        <v>14.621018409729</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1842" t="n">
-        <v>14.5543279647827</v>
+        <v>14.5543298721313</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1845" t="n">
-        <v>14.5710020065308</v>
+        <v>14.5710010528564</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1846" t="n">
-        <v>14.8210763931274</v>
+        <v>14.8210744857788</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1850" t="n">
-        <v>15.671329498291</v>
+        <v>15.6713285446167</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1854" t="n">
-        <v>15.4879388809204</v>
+        <v>15.487940788269</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G1858" t="n">
-        <v>15.1044940948486</v>
+        <v>15.1044931411743</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1861" t="n">
-        <v>14.3042554855347</v>
+        <v>14.3042545318604</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1862" t="n">
-        <v>14.0375099182129</v>
+        <v>14.0375089645386</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1865" t="n">
-        <v>14.0375099182129</v>
+        <v>14.0375089645386</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1870" t="n">
-        <v>14.5209875106812</v>
+        <v>14.5209865570068</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1873" t="n">
-        <v>14.1041965484619</v>
+        <v>14.1041955947876</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1899" t="n">
-        <v>13.5218658447266</v>
+        <v>13.5218667984009</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1906" t="n">
-        <v>13.1760377883911</v>
+        <v>13.1760387420654</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1921" t="n">
-        <v>13.418119430542</v>
+        <v>13.4181184768677</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1926" t="n">
-        <v>13.418119430542</v>
+        <v>13.4181184768677</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1945" t="n">
-        <v>13.1760377883911</v>
+        <v>13.1760387420654</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1957" t="n">
-        <v>13.2279119491577</v>
+        <v>13.227912902832</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1967" t="n">
-        <v>12.3460512161255</v>
+        <v>12.3460521697998</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>6.51999998092651</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>79622</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>6.44000005722046</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>6.05000019073486</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>6.07999992370605</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>206332</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>6.30999994277954</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>6.15999984741211</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>6.30000019073486</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>105757</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>6.32000017166138</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>6.21999979019165</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>6.26000022888184</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>93125</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>6.32999992370605</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>6.19000005722046</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>6.28999996185303</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>6.28999996185303</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>6.28999996185303</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>82386</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>6.38000011444092</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>6.26999998092651</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>6.36999988555908</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>59217</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>6.34000015258789</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>6.30999994277954</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>6.34000015258789</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G2" t="n">
-        <v>3.92318487167358</v>
+        <v>3.92318391799927</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.90674138069153</v>
+        <v>3.90674161911011</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G4" t="n">
-        <v>3.82452988624573</v>
+        <v>3.82453012466431</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>3.71600842475891</v>
+        <v>3.71600914001465</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6699697971344</v>
+        <v>3.66996955871582</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G7" t="n">
-        <v>3.60091114044189</v>
+        <v>3.60091090202332</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>3.64695048332214</v>
+        <v>3.64695072174072</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G10" t="n">
-        <v>3.68970012664795</v>
+        <v>3.68970131874084</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.56500005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>3.66010403633118</v>
+        <v>3.66010332107544</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.57789158821106</v>
+        <v>3.57789206504822</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G13" t="n">
-        <v>3.55816006660461</v>
+        <v>3.55816078186035</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G15" t="n">
-        <v>3.54500603675842</v>
+        <v>3.545006275177</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.61735343933105</v>
+        <v>3.61735367774963</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.5</v>
       </c>
       <c r="G17" t="n">
-        <v>3.61735343933105</v>
+        <v>3.61735367774963</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.59433484077454</v>
+        <v>3.59433388710022</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>3.55158376693726</v>
+        <v>3.5515832901001</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>3.55158376693726</v>
+        <v>3.5515832901001</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G22" t="n">
-        <v>3.6370837688446</v>
+        <v>3.6370849609375</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.5</v>
       </c>
       <c r="G23" t="n">
-        <v>3.61735343933105</v>
+        <v>3.61735367774963</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>3.49239110946655</v>
+        <v>3.49239087104797</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>3.47923588752747</v>
+        <v>3.47923612594604</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>3.39373540878296</v>
+        <v>3.39373517036438</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G31" t="n">
-        <v>3.30823469161987</v>
+        <v>3.30823421478271</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G32" t="n">
-        <v>3.40688872337341</v>
+        <v>3.40688896179199</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>3.49239110946655</v>
+        <v>3.49239087104797</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50554442405701</v>
+        <v>3.50554394721985</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>3.44306254386902</v>
+        <v>3.4430627822876</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42333173751831</v>
+        <v>3.42333221435547</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>3.40031266212463</v>
+        <v>3.40031242370605</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.45621681213379</v>
+        <v>3.45621752738953</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.47594809532166</v>
+        <v>3.47594785690308</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>3.49567866325378</v>
+        <v>3.49567937850952</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>3.47923588752747</v>
+        <v>3.47923612594604</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G47" t="n">
-        <v>3.43977475166321</v>
+        <v>3.43977403640747</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>3.46608281135559</v>
+        <v>3.46608304977417</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>3.53842949867249</v>
+        <v>3.53842997550964</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G52" t="n">
-        <v>3.6765468120575</v>
+        <v>3.67654728889465</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G53" t="n">
-        <v>3.6765468120575</v>
+        <v>3.67654728889465</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G55" t="n">
-        <v>3.75218224525452</v>
+        <v>3.75218176841736</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>3.73902797698975</v>
+        <v>3.7390284538269</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>3.81466436386108</v>
+        <v>3.81466388702393</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G60" t="n">
-        <v>3.7883563041687</v>
+        <v>3.78835535049438</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3.78177833557129</v>
+        <v>3.78177928924561</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>3.80808687210083</v>
+        <v>3.80808639526367</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G64" t="n">
-        <v>3.79493260383606</v>
+        <v>3.7949321269989</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G65" t="n">
-        <v>3.85412621498108</v>
+        <v>3.85412573814392</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G66" t="n">
-        <v>3.82452988624573</v>
+        <v>3.82453012466431</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.74560570716858</v>
+        <v>3.74560523033142</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G70" t="n">
-        <v>3.82781791687012</v>
+        <v>3.8278181552887</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G71" t="n">
-        <v>3.81466436386108</v>
+        <v>3.81466388702393</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G72" t="n">
-        <v>3.82781791687012</v>
+        <v>3.8278181552887</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.75500011444092</v>
       </c>
       <c r="G73" t="n">
-        <v>3.78506731987</v>
+        <v>3.78506755828857</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G74" t="n">
-        <v>3.83110594749451</v>
+        <v>3.83110547065735</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G75" t="n">
-        <v>3.84097194671631</v>
+        <v>3.84097146987915</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G76" t="n">
-        <v>3.81466436386108</v>
+        <v>3.81466388702393</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>3.82452988624573</v>
+        <v>3.82453012466431</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.84754872322083</v>
+        <v>3.84754920005798</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>3.81466436386108</v>
+        <v>3.81466388702393</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G81" t="n">
-        <v>3.83110594749451</v>
+        <v>3.83110547065735</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84097194671631</v>
+        <v>3.84097146987915</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.85741400718689</v>
+        <v>3.85741353034973</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G85" t="n">
-        <v>3.7883563041687</v>
+        <v>3.78835535049438</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.75500011444092</v>
       </c>
       <c r="G86" t="n">
-        <v>3.78506731987</v>
+        <v>3.78506755828857</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>3.75875926017761</v>
+        <v>3.75875902175903</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.73902797698975</v>
+        <v>3.7390284538269</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.5</v>
       </c>
       <c r="G90" t="n">
-        <v>3.77333092689514</v>
+        <v>3.7733314037323</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>3.75960993766785</v>
+        <v>3.75961065292358</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>3.74588871002197</v>
+        <v>3.74588894844055</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G93" t="n">
-        <v>3.72530674934387</v>
+        <v>3.72530651092529</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.5</v>
       </c>
       <c r="G94" t="n">
-        <v>3.77333092689514</v>
+        <v>3.7733314037323</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.74931979179382</v>
+        <v>3.74931907653809</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>3.76304054260254</v>
+        <v>3.76304006576538</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G97" t="n">
-        <v>3.78019189834595</v>
+        <v>3.78019142150879</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>3.78705215454102</v>
+        <v>3.78705239295959</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G99" t="n">
-        <v>3.77676129341125</v>
+        <v>3.7767608165741</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.82821607589722</v>
+        <v>3.82821583747864</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G101" t="n">
-        <v>3.83850646018982</v>
+        <v>3.83850693702698</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.84536695480347</v>
+        <v>3.8453676700592</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G104" t="n">
-        <v>3.90711331367493</v>
+        <v>3.90711283683777</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G107" t="n">
-        <v>3.93798542022705</v>
+        <v>3.93798637390137</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.92083406448364</v>
+        <v>3.92083358764648</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87624001502991</v>
+        <v>3.87624049186707</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>3.8899610042572</v>
+        <v>3.88996148109436</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.625</v>
       </c>
       <c r="G112" t="n">
-        <v>3.8590886592865</v>
+        <v>3.85908818244934</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G114" t="n">
-        <v>3.75960993766785</v>
+        <v>3.75961065292358</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>3.6704216003418</v>
+        <v>3.67042207717896</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G117" t="n">
-        <v>3.64640974998474</v>
+        <v>3.64641046524048</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G118" t="n">
-        <v>3.63954877853394</v>
+        <v>3.63954949378967</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79048299789429</v>
+        <v>3.79048275947571</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G120" t="n">
-        <v>3.83850646018982</v>
+        <v>3.83850693702698</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>3.8076343536377</v>
+        <v>3.80763363838196</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>3.83507680892944</v>
+        <v>3.8350772857666</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>3.91740345954895</v>
+        <v>3.91740417480469</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>3.78019189834595</v>
+        <v>3.78019142150879</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G125" t="n">
-        <v>3.64984011650085</v>
+        <v>3.64984059333801</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G126" t="n">
-        <v>3.69786405563354</v>
+        <v>3.69786429405212</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.71844601631165</v>
+        <v>3.71844625473022</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>3.75960993766785</v>
+        <v>3.75961065292358</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>3.75617980957031</v>
+        <v>3.75617957115173</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>3.74588871002197</v>
+        <v>3.74588894844055</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.71158528327942</v>
+        <v>3.71158576011658</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G132" t="n">
-        <v>3.69443416595459</v>
+        <v>3.69443440437317</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G133" t="n">
-        <v>3.72873735427856</v>
+        <v>3.72873711585999</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>3.73902797698975</v>
+        <v>3.73902750015259</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G135" t="n">
-        <v>3.70472550392151</v>
+        <v>3.70472526550293</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>3.71844601631165</v>
+        <v>3.71844625473022</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G138" t="n">
-        <v>3.78019189834595</v>
+        <v>3.78019142150879</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G139" t="n">
-        <v>3.78362202644348</v>
+        <v>3.7836217880249</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G141" t="n">
-        <v>3.7939121723175</v>
+        <v>3.7939133644104</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G142" t="n">
-        <v>3.83850646018982</v>
+        <v>3.83850693702698</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G143" t="n">
-        <v>3.83507680892944</v>
+        <v>3.8350772857666</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>3.80077385902405</v>
+        <v>3.80077362060547</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>3.86251854896545</v>
+        <v>3.86251926422119</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>3.8076343536377</v>
+        <v>3.80763363838196</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G147" t="n">
-        <v>3.88310122489929</v>
+        <v>3.88310050964355</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G148" t="n">
-        <v>3.90368294715881</v>
+        <v>3.90368318557739</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G150" t="n">
-        <v>3.78362202644348</v>
+        <v>3.7836217880249</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>3.73902797698975</v>
+        <v>3.73902750015259</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>3.7321674823761</v>
+        <v>3.73216795921326</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G153" t="n">
-        <v>3.71158528327942</v>
+        <v>3.71158576011658</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.70129466056824</v>
+        <v>3.70129489898682</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>3.71844601631165</v>
+        <v>3.71844625473022</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G156" t="n">
-        <v>3.71158528327942</v>
+        <v>3.71158576011658</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>3.70472550392151</v>
+        <v>3.70472526550293</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>3.70472550392151</v>
+        <v>3.70472526550293</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G159" t="n">
-        <v>3.69786405563354</v>
+        <v>3.69786429405212</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G160" t="n">
-        <v>3.6704216003418</v>
+        <v>3.67042207717896</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>3.71158528327942</v>
+        <v>3.71158576011658</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G162" t="n">
-        <v>3.66013073921204</v>
+        <v>3.66013169288635</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>3.65327072143555</v>
+        <v>3.65327048301697</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>3.63611912727356</v>
+        <v>3.63611888885498</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G170" t="n">
-        <v>3.63611912727356</v>
+        <v>3.63611888885498</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>3.61553764343262</v>
+        <v>3.61553740501404</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>3.63611912727356</v>
+        <v>3.63611888885498</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G173" t="n">
-        <v>3.63954877853394</v>
+        <v>3.63954949378967</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G174" t="n">
-        <v>3.66356158256531</v>
+        <v>3.66356110572815</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G175" t="n">
-        <v>3.71158528327942</v>
+        <v>3.71158576011658</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G177" t="n">
-        <v>3.70815467834473</v>
+        <v>3.70815563201904</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.61896800994873</v>
+        <v>3.61896753311157</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G181" t="n">
-        <v>3.62925791740417</v>
+        <v>3.62925839424133</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62239766120911</v>
+        <v>3.62239789962769</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G183" t="n">
-        <v>3.72530674934387</v>
+        <v>3.72530651092529</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G184" t="n">
-        <v>3.66356158256531</v>
+        <v>3.66356110572815</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>3.6258282661438</v>
+        <v>3.62582802772522</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G186" t="n">
-        <v>3.62239766120911</v>
+        <v>3.62239789962769</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G187" t="n">
-        <v>3.64984011650085</v>
+        <v>3.64984059333801</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G188" t="n">
-        <v>3.63954877853394</v>
+        <v>3.63954949378967</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>3.54693150520325</v>
+        <v>3.54693102836609</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G190" t="n">
-        <v>3.53321003913879</v>
+        <v>3.53321051597595</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G191" t="n">
-        <v>3.55379128456116</v>
+        <v>3.55379152297974</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G192" t="n">
-        <v>3.55379128456116</v>
+        <v>3.55379152297974</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.51262760162354</v>
+        <v>3.51262736320496</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G194" t="n">
-        <v>3.51262760162354</v>
+        <v>3.51262736320496</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G196" t="n">
-        <v>3.51948928833008</v>
+        <v>3.51948833465576</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G197" t="n">
-        <v>3.50919771194458</v>
+        <v>3.50919795036316</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G198" t="n">
-        <v>3.54007077217102</v>
+        <v>3.54007005691528</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>3.63268852233887</v>
+        <v>3.63268804550171</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G200" t="n">
-        <v>3.76304054260254</v>
+        <v>3.76304006576538</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G201" t="n">
-        <v>3.7321674823761</v>
+        <v>3.73216795921326</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G202" t="n">
-        <v>3.71844601631165</v>
+        <v>3.71844625473022</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G203" t="n">
-        <v>3.74931979179382</v>
+        <v>3.74931907653809</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>3.8076343536377</v>
+        <v>3.80763363838196</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G205" t="n">
-        <v>3.8076343536377</v>
+        <v>3.80763363838196</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>3.82821607589722</v>
+        <v>3.82821583747864</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G208" t="n">
-        <v>3.86937928199768</v>
+        <v>3.8693790435791</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G209" t="n">
-        <v>3.87967085838318</v>
+        <v>3.87967038154602</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G210" t="n">
-        <v>3.87967085838318</v>
+        <v>3.87967038154602</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>5.625</v>
       </c>
       <c r="G211" t="n">
-        <v>3.8590886592865</v>
+        <v>3.85908818244934</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>3.79048299789429</v>
+        <v>3.79048275947571</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>3.77676129341125</v>
+        <v>3.7767608165741</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>3.78362202644348</v>
+        <v>3.7836217880249</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G215" t="n">
-        <v>3.76647043228149</v>
+        <v>3.76646995544434</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G217" t="n">
-        <v>3.78362202644348</v>
+        <v>3.7836217880249</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G218" t="n">
-        <v>3.76647043228149</v>
+        <v>3.76646995544434</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>3.76647043228149</v>
+        <v>3.76646995544434</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G220" t="n">
-        <v>3.68414258956909</v>
+        <v>3.68414306640625</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>3.71501612663269</v>
+        <v>3.71501660346985</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G222" t="n">
-        <v>3.73902797698975</v>
+        <v>3.73902750015259</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G223" t="n">
-        <v>3.74931979179382</v>
+        <v>3.74931907653809</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G225" t="n">
-        <v>3.71158528327942</v>
+        <v>3.71158576011658</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G226" t="n">
-        <v>3.73559808731079</v>
+        <v>3.73559761047363</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>3.70129466056824</v>
+        <v>3.70129489898682</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G228" t="n">
-        <v>3.66356158256531</v>
+        <v>3.66356110572815</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.25</v>
       </c>
       <c r="G229" t="n">
-        <v>3.60181593894958</v>
+        <v>3.60181617736816</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G230" t="n">
-        <v>3.64984011650085</v>
+        <v>3.64984059333801</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G231" t="n">
-        <v>3.68414258956909</v>
+        <v>3.68414306640625</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G232" t="n">
-        <v>3.71158528327942</v>
+        <v>3.71158576011658</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>3.70472550392151</v>
+        <v>3.70472526550293</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G234" t="n">
-        <v>3.64640974998474</v>
+        <v>3.64641046524048</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G235" t="n">
-        <v>3.64984011650085</v>
+        <v>3.64984059333801</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>3.70129466056824</v>
+        <v>3.70129489898682</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>3.65327072143555</v>
+        <v>3.65327048301697</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.25</v>
       </c>
       <c r="G238" t="n">
-        <v>3.60181593894958</v>
+        <v>3.60181617736816</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G240" t="n">
-        <v>3.69443416595459</v>
+        <v>3.69443440437317</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.80077385902405</v>
+        <v>3.80077362060547</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G243" t="n">
-        <v>3.7939121723175</v>
+        <v>3.7939133644104</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>3.78705215454102</v>
+        <v>3.78705239295959</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>3.78705215454102</v>
+        <v>3.78705239295959</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G246" t="n">
-        <v>3.76304054260254</v>
+        <v>3.76304006576538</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G247" t="n">
-        <v>3.72530674934387</v>
+        <v>3.72530651092529</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G248" t="n">
-        <v>3.7939121723175</v>
+        <v>3.7939133644104</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G249" t="n">
-        <v>3.76647043228149</v>
+        <v>3.76646995544434</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G250" t="n">
-        <v>3.74245858192444</v>
+        <v>3.74245834350586</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>3.76647043228149</v>
+        <v>3.76646995544434</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>3.74588871002197</v>
+        <v>3.74588894844055</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G253" t="n">
-        <v>3.72530674934387</v>
+        <v>3.72530651092529</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G254" t="n">
-        <v>3.76647043228149</v>
+        <v>3.76646995544434</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G255" t="n">
-        <v>3.73559808731079</v>
+        <v>3.73559761047363</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.74931979179382</v>
+        <v>3.74931907653809</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>3.78705215454102</v>
+        <v>3.78705239295959</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G260" t="n">
-        <v>3.87967085838318</v>
+        <v>3.87967038154602</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G261" t="n">
-        <v>3.92426347732544</v>
+        <v>3.92426419258118</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>3.91740345954895</v>
+        <v>3.91740417480469</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G263" t="n">
-        <v>3.96542835235596</v>
+        <v>3.96542811393738</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>3.97914981842041</v>
+        <v>3.97914958000183</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>3.93112516403198</v>
+        <v>3.9311249256134</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>3.97228860855103</v>
+        <v>3.97228765487671</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G268" t="n">
-        <v>3.97228860855103</v>
+        <v>3.97228765487671</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G269" t="n">
-        <v>3.98944067955017</v>
+        <v>3.98944044113159</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G270" t="n">
-        <v>3.96542835235596</v>
+        <v>3.96542811393738</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95856714248657</v>
+        <v>3.95856690406799</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G273" t="n">
-        <v>3.88310122489929</v>
+        <v>3.88310050964355</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>3.91740345954895</v>
+        <v>3.91740417480469</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>3.90368294715881</v>
+        <v>3.90368318557739</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G277" t="n">
-        <v>3.93798542022705</v>
+        <v>3.93798637390137</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>3.91740345954895</v>
+        <v>3.91740417480469</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G279" t="n">
-        <v>3.90711331367493</v>
+        <v>3.90711283683777</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.625</v>
       </c>
       <c r="G282" t="n">
-        <v>3.8590886592865</v>
+        <v>3.85908818244934</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G283" t="n">
-        <v>3.86937928199768</v>
+        <v>3.8693790435791</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>3.87624001502991</v>
+        <v>3.87624049186707</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G285" t="n">
-        <v>3.92769432067871</v>
+        <v>3.92769455909729</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>3.95856714248657</v>
+        <v>3.95856690406799</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.75</v>
       </c>
       <c r="G287" t="n">
-        <v>3.94484567642212</v>
+        <v>3.94484639167786</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G288" t="n">
-        <v>3.98600959777832</v>
+        <v>3.98600912094116</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>5.80499982833862</v>
       </c>
       <c r="G289" t="n">
-        <v>3.98257923126221</v>
+        <v>3.98257946968079</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>3.98944067955017</v>
+        <v>3.98944044113159</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G292" t="n">
-        <v>4.006591796875</v>
+        <v>4.00659132003784</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G294" t="n">
-        <v>3.98944067955017</v>
+        <v>3.98944044113159</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>4.06147575378418</v>
+        <v>4.0614767074585</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G298" t="n">
-        <v>4.06147575378418</v>
+        <v>4.0614767074585</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G299" t="n">
-        <v>4.0374641418457</v>
+        <v>4.03746461868286</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6</v>
       </c>
       <c r="G300" t="n">
-        <v>4.11636161804199</v>
+        <v>4.11636114120483</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G301" t="n">
-        <v>4.09234952926636</v>
+        <v>4.0923490524292</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6</v>
       </c>
       <c r="G302" t="n">
-        <v>4.11636161804199</v>
+        <v>4.11636114120483</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>4.2192702293396</v>
+        <v>4.21927070617676</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G306" t="n">
-        <v>4.23985147476196</v>
+        <v>4.2398509979248</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G307" t="n">
-        <v>4.22613096237183</v>
+        <v>4.22613048553467</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G308" t="n">
-        <v>4.18496656417847</v>
+        <v>4.18496704101562</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>4.17810583114624</v>
+        <v>4.17810726165771</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G310" t="n">
-        <v>4.23985147476196</v>
+        <v>4.2398509979248</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>4.25357294082642</v>
+        <v>4.25357341766357</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>4.37706470489502</v>
+        <v>4.3770637512207</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>4.58974313735962</v>
+        <v>4.58974266052246</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>4.76811790466309</v>
+        <v>4.7681188583374</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>7</v>
       </c>
       <c r="G315" t="n">
-        <v>4.80242109298706</v>
+        <v>4.80242156982422</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G316" t="n">
-        <v>5.04254245758057</v>
+        <v>5.04254293441772</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>5.07341480255127</v>
+        <v>5.07341432571411</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>4.94306325912476</v>
+        <v>4.94306373596191</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G322" t="n">
-        <v>4.92591238021851</v>
+        <v>4.92591142654419</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G324" t="n">
-        <v>4.96707487106323</v>
+        <v>4.96707582473755</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.95678472518921</v>
+        <v>4.95678520202637</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>5.00137948989868</v>
+        <v>5.00137901306152</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>5.00137948989868</v>
+        <v>5.00137901306152</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G334" t="n">
-        <v>4.9945182800293</v>
+        <v>4.99451875686646</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>5.09399700164795</v>
+        <v>5.09399747848511</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G338" t="n">
-        <v>5.43359756469727</v>
+        <v>5.43359661102295</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G339" t="n">
-        <v>5.35126924514771</v>
+        <v>5.35127019882202</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>5.20033597946167</v>
+        <v>5.20033645629883</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>7.75</v>
       </c>
       <c r="G341" t="n">
-        <v>5.31696701049805</v>
+        <v>5.31696653366089</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G342" t="n">
-        <v>5.21405792236328</v>
+        <v>5.21405744552612</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>5.28266382217407</v>
+        <v>5.28266334533691</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G345" t="n">
-        <v>5.44781637191772</v>
+        <v>5.44781684875488</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>5.52224969863892</v>
+        <v>5.52225017547607</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G348" t="n">
-        <v>5.45845031738281</v>
+        <v>5.45844984054565</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G349" t="n">
-        <v>5.45490598678589</v>
+        <v>5.45490503311157</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>5.44781637191772</v>
+        <v>5.44781684875488</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G351" t="n">
-        <v>5.43363857269287</v>
+        <v>5.43363904953003</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G353" t="n">
-        <v>5.25996017456055</v>
+        <v>5.25996065139771</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>5.39464950561523</v>
+        <v>5.39464998245239</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.29540586471558</v>
+        <v>5.29540491104126</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G361" t="n">
-        <v>5.21742725372314</v>
+        <v>5.2174277305603</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G362" t="n">
-        <v>5.27413892745972</v>
+        <v>5.27413845062256</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.5</v>
       </c>
       <c r="G365" t="n">
-        <v>5.31667232513428</v>
+        <v>5.31667184829712</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>5.28831624984741</v>
+        <v>5.28831577301025</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G369" t="n">
-        <v>5.33439445495605</v>
+        <v>5.3343939781189</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G371" t="n">
-        <v>5.45845031738281</v>
+        <v>5.45844984054565</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G372" t="n">
-        <v>5.43718385696411</v>
+        <v>5.43718290328979</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>5.25287199020386</v>
+        <v>5.25287103652954</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.35211610794067</v>
+        <v>5.35211563110352</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>5.38756132125854</v>
+        <v>5.38756084442139</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>5.38756132125854</v>
+        <v>5.38756084442139</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G381" t="n">
-        <v>5.34502744674683</v>
+        <v>5.34502792358398</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>5.38756132125854</v>
+        <v>5.38756084442139</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G383" t="n">
-        <v>5.18907165527344</v>
+        <v>5.1890721321106</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G384" t="n">
-        <v>5.21388292312622</v>
+        <v>5.21388244628906</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G385" t="n">
-        <v>5.15717077255249</v>
+        <v>5.15717172622681</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.13235998153687</v>
+        <v>5.13236141204834</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G387" t="n">
-        <v>5.0047607421875</v>
+        <v>5.00476026535034</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>4.97640419006348</v>
+        <v>4.97640562057495</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G392" t="n">
-        <v>5.27413892745972</v>
+        <v>5.27413845062256</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>5.24932813644409</v>
+        <v>5.24932765960693</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G395" t="n">
-        <v>5.22097158432007</v>
+        <v>5.22097206115723</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G396" t="n">
-        <v>5.08982753753662</v>
+        <v>5.08982706069946</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G398" t="n">
-        <v>5.30958271026611</v>
+        <v>5.30958318710327</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>5.25641584396362</v>
+        <v>5.25641632080078</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G400" t="n">
-        <v>5.26705026626587</v>
+        <v>5.26704931259155</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>5.25641584396362</v>
+        <v>5.25641632080078</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G402" t="n">
-        <v>5.28122711181641</v>
+        <v>5.28122758865356</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G403" t="n">
-        <v>5.32376050949097</v>
+        <v>5.32376098632812</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>5.1961612701416</v>
+        <v>5.19616079330444</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>5.34148263931274</v>
+        <v>5.34148359298706</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G410" t="n">
-        <v>5.41591644287109</v>
+        <v>5.41591739654541</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>5.45845031738281</v>
+        <v>5.45844984054565</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>5.45845031738281</v>
+        <v>5.45844984054565</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>5.40173816680908</v>
+        <v>5.40173864364624</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>5.25641584396362</v>
+        <v>5.25641632080078</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>5.37692785263062</v>
+        <v>5.37692737579346</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G417" t="n">
-        <v>5.41591644287109</v>
+        <v>5.41591739654541</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.38756132125854</v>
+        <v>5.38756084442139</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G421" t="n">
-        <v>5.42300462722778</v>
+        <v>5.42300510406494</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G424" t="n">
-        <v>5.32376050949097</v>
+        <v>5.32376098632812</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>5.35211610794067</v>
+        <v>5.35211563110352</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>5.36983823776245</v>
+        <v>5.36983871459961</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G430" t="n">
-        <v>5.41591644287109</v>
+        <v>5.41591739654541</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>5.38756132125854</v>
+        <v>5.38756084442139</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>5.44072771072388</v>
+        <v>5.44072723388672</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G433" t="n">
-        <v>5.33439445495605</v>
+        <v>5.3343939781189</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G434" t="n">
-        <v>5.34148263931274</v>
+        <v>5.34148359298706</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G435" t="n">
-        <v>5.38756132125854</v>
+        <v>5.38756084442139</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G436" t="n">
-        <v>5.42654991149902</v>
+        <v>5.42654943466187</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>5.38756132125854</v>
+        <v>5.38756084442139</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G439" t="n">
-        <v>5.52224969863892</v>
+        <v>5.52225017547607</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G441" t="n">
-        <v>5.62503957748413</v>
+        <v>5.62503910064697</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G442" t="n">
-        <v>5.75618314743042</v>
+        <v>5.75618362426758</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G443" t="n">
-        <v>5.77036094665527</v>
+        <v>5.77036190032959</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>5.81289434432983</v>
+        <v>5.81289482116699</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G448" t="n">
-        <v>5.75618314743042</v>
+        <v>5.75618362426758</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G450" t="n">
-        <v>5.71364974975586</v>
+        <v>5.71365070343018</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G453" t="n">
-        <v>5.71364974975586</v>
+        <v>5.71365070343018</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G456" t="n">
-        <v>5.66757202148438</v>
+        <v>5.66757154464722</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8</v>
       </c>
       <c r="G457" t="n">
-        <v>5.6711163520813</v>
+        <v>5.67111682891846</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G458" t="n">
-        <v>5.69947195053101</v>
+        <v>5.69947242736816</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G459" t="n">
-        <v>5.69947195053101</v>
+        <v>5.69947242736816</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G461" t="n">
-        <v>5.68175077438354</v>
+        <v>5.68175029754639</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G464" t="n">
-        <v>5.69238328933716</v>
+        <v>5.6923828125</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>5.58605051040649</v>
+        <v>5.58605003356934</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>5.56123876571655</v>
+        <v>5.56123828887939</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G468" t="n">
-        <v>5.50098276138306</v>
+        <v>5.50098371505737</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>5.69947195053101</v>
+        <v>5.69947242736816</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G471" t="n">
-        <v>5.71719360351562</v>
+        <v>5.71719408035278</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>8</v>
       </c>
       <c r="G473" t="n">
-        <v>5.6711163520813</v>
+        <v>5.67111682891846</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>7.85500001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>5.5683274269104</v>
+        <v>5.56832695007324</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G480" t="n">
-        <v>5.59313869476318</v>
+        <v>5.59313821792603</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>5.46199464797974</v>
+        <v>5.46199369430542</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>5.43718385696411</v>
+        <v>5.43718290328979</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>5.43718385696411</v>
+        <v>5.43718290328979</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8</v>
       </c>
       <c r="G488" t="n">
-        <v>5.6711163520813</v>
+        <v>5.67111682891846</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>5.63567161560059</v>
+        <v>5.63567113876343</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8</v>
       </c>
       <c r="G495" t="n">
-        <v>5.6711163520813</v>
+        <v>5.67111682891846</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G498" t="n">
-        <v>5.50098276138306</v>
+        <v>5.50098371505737</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.08500003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>5.73137283325195</v>
+        <v>5.73137235641479</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G500" t="n">
-        <v>5.75263929367065</v>
+        <v>5.7526388168335</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G501" t="n">
-        <v>5.74909400939941</v>
+        <v>5.74909496307373</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G502" t="n">
-        <v>5.77745008468628</v>
+        <v>5.77744960784912</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G503" t="n">
-        <v>5.77745008468628</v>
+        <v>5.77744960784912</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>5.77036094665527</v>
+        <v>5.77036190032959</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G506" t="n">
-        <v>5.81289434432983</v>
+        <v>5.81289482116699</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G507" t="n">
-        <v>5.81289434432983</v>
+        <v>5.81289482116699</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G511" t="n">
-        <v>5.77036094665527</v>
+        <v>5.77036190032959</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G512" t="n">
-        <v>5.83416128158569</v>
+        <v>5.83416080474854</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>5.81289434432983</v>
+        <v>5.81289482116699</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G522" t="n">
-        <v>5.85542821884155</v>
+        <v>5.85542917251587</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G523" t="n">
-        <v>5.85542821884155</v>
+        <v>5.85542917251587</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G524" t="n">
-        <v>5.86251783370972</v>
+        <v>5.8625168800354</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>8.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.02556228637695</v>
+        <v>6.02556133270264</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G529" t="n">
-        <v>5.96176147460938</v>
+        <v>5.96176099777222</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G530" t="n">
-        <v>5.94758415222168</v>
+        <v>5.94758367538452</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G531" t="n">
-        <v>5.94758415222168</v>
+        <v>5.94758367538452</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>5.75618314743042</v>
+        <v>5.75618362426758</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>5.62858390808105</v>
+        <v>5.6285834312439</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>8</v>
       </c>
       <c r="G538" t="n">
-        <v>5.6711163520813</v>
+        <v>5.67111682891846</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>5.69947195053101</v>
+        <v>5.69947242736816</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8</v>
       </c>
       <c r="G540" t="n">
-        <v>5.6711163520813</v>
+        <v>5.67111682891846</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G541" t="n">
-        <v>5.77036094665527</v>
+        <v>5.77036190032959</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G542" t="n">
-        <v>5.77036094665527</v>
+        <v>5.77036190032959</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>5.79162836074829</v>
+        <v>5.79162788391113</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G544" t="n">
-        <v>5.77745008468628</v>
+        <v>5.77744960784912</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G547" t="n">
-        <v>5.77036094665527</v>
+        <v>5.77036190032959</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>5.79162836074829</v>
+        <v>5.79162788391113</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G550" t="n">
-        <v>5.67820596694946</v>
+        <v>5.6782054901123</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G551" t="n">
-        <v>5.79871654510498</v>
+        <v>5.7987174987793</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G552" t="n">
-        <v>5.81289434432983</v>
+        <v>5.81289482116699</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>5.81289434432983</v>
+        <v>5.81289482116699</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G554" t="n">
-        <v>5.77745008468628</v>
+        <v>5.77744960784912</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="n">
-        <v>5.71364974975586</v>
+        <v>5.71365070343018</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G557" t="n">
-        <v>5.79162836074829</v>
+        <v>5.79162788391113</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G558" t="n">
-        <v>5.86251783370972</v>
+        <v>5.8625168800354</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G560" t="n">
-        <v>5.94049453735352</v>
+        <v>5.94049501419067</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G561" t="n">
-        <v>5.96176147460938</v>
+        <v>5.96176099777222</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G562" t="n">
-        <v>5.97593975067139</v>
+        <v>5.97593927383423</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G564" t="n">
-        <v>5.9263162612915</v>
+        <v>5.92631673812866</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G565" t="n">
-        <v>5.80580520629883</v>
+        <v>5.80580568313599</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G568" t="n">
-        <v>5.85542821884155</v>
+        <v>5.85542917251587</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G571" t="n">
-        <v>5.83416128158569</v>
+        <v>5.83416080474854</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G575" t="n">
-        <v>5.97593975067139</v>
+        <v>5.97593927383423</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G576" t="n">
-        <v>5.9263162612915</v>
+        <v>5.92631673812866</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G578" t="n">
-        <v>5.85542821884155</v>
+        <v>5.85542917251587</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G579" t="n">
-        <v>5.86251783370972</v>
+        <v>5.8625168800354</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G583" t="n">
-        <v>5.86251783370972</v>
+        <v>5.8625168800354</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G584" t="n">
-        <v>5.77745008468628</v>
+        <v>5.77744960784912</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G585" t="n">
-        <v>5.85542821884155</v>
+        <v>5.85542917251587</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>5.8766942024231</v>
+        <v>5.87669467926025</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G592" t="n">
-        <v>5.94758415222168</v>
+        <v>5.94758367538452</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>5.90505075454712</v>
+        <v>5.90504932403564</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>5.99720621109009</v>
+        <v>5.99720573425293</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>5.99720621109009</v>
+        <v>5.99720573425293</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G597" t="n">
-        <v>5.9263162612915</v>
+        <v>5.92631673812866</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>5.94049453735352</v>
+        <v>5.94049501419067</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>5.99011707305908</v>
+        <v>5.99011659622192</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G602" t="n">
-        <v>6.0964503288269</v>
+        <v>6.09645080566406</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>6.13326501846313</v>
+        <v>6.13326406478882</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G608" t="n">
-        <v>6.08908843994141</v>
+        <v>6.08908748626709</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G609" t="n">
-        <v>6.08172464370728</v>
+        <v>6.08172559738159</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G610" t="n">
-        <v>6.03018379211426</v>
+        <v>6.03018426895142</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G611" t="n">
-        <v>6.08908843994141</v>
+        <v>6.08908748626709</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G612" t="n">
-        <v>6.00073289871216</v>
+        <v>6.000732421875</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G613" t="n">
-        <v>5.97128105163574</v>
+        <v>5.97128200531006</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>5.85347509384155</v>
+        <v>5.85347557067871</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>5.87556457519531</v>
+        <v>5.87556409835815</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G618" t="n">
-        <v>6.04490995407104</v>
+        <v>6.04491090774536</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G619" t="n">
-        <v>6.08172464370728</v>
+        <v>6.08172559738159</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G620" t="n">
-        <v>6.06699848175049</v>
+        <v>6.06699895858765</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G621" t="n">
-        <v>6.08908843994141</v>
+        <v>6.08908748626709</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G624" t="n">
-        <v>6.18480443954468</v>
+        <v>6.18480491638184</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>6.00809621810913</v>
+        <v>6.00809574127197</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G627" t="n">
-        <v>6.13326501846313</v>
+        <v>6.13326406478882</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G628" t="n">
-        <v>6.06699848175049</v>
+        <v>6.06699895858765</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G630" t="n">
-        <v>6.0228214263916</v>
+        <v>6.02282238006592</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.00809621810913</v>
+        <v>6.00809574127197</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G632" t="n">
-        <v>6.03018379211426</v>
+        <v>6.03018426895142</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G633" t="n">
-        <v>6.0228214263916</v>
+        <v>6.02282238006592</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G634" t="n">
-        <v>5.97128105163574</v>
+        <v>5.97128200531006</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G635" t="n">
-        <v>5.87556457519531</v>
+        <v>5.87556409835815</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G637" t="n">
-        <v>5.87556457519531</v>
+        <v>5.87556409835815</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>5.83138799667358</v>
+        <v>5.83138751983643</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G640" t="n">
-        <v>5.80929851531982</v>
+        <v>5.80929803848267</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G642" t="n">
-        <v>5.95655632019043</v>
+        <v>5.95655584335327</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G643" t="n">
-        <v>5.93446683883667</v>
+        <v>5.93446826934814</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G644" t="n">
-        <v>5.91237878799438</v>
+        <v>5.91237783432007</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G646" t="n">
-        <v>5.90501594543457</v>
+        <v>5.90501642227173</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G647" t="n">
-        <v>5.96391916275024</v>
+        <v>5.96391868591309</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G648" t="n">
-        <v>5.92710494995117</v>
+        <v>5.92710447311401</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G649" t="n">
-        <v>5.93446683883667</v>
+        <v>5.93446826934814</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G650" t="n">
-        <v>5.95655632019043</v>
+        <v>5.95655584335327</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G651" t="n">
-        <v>5.95655632019043</v>
+        <v>5.95655584335327</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G653" t="n">
-        <v>5.82402420043945</v>
+        <v>5.82402467727661</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>5.76512098312378</v>
+        <v>5.76512145996094</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>5.83138799667358</v>
+        <v>5.83138751983643</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G658" t="n">
-        <v>5.97128105163574</v>
+        <v>5.97128200531006</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G661" t="n">
-        <v>5.96391916275024</v>
+        <v>5.96391868591309</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G663" t="n">
-        <v>5.92710494995117</v>
+        <v>5.92710447311401</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G664" t="n">
-        <v>5.91237878799438</v>
+        <v>5.91237783432007</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>5.91237878799438</v>
+        <v>5.91237783432007</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>5.74303293228149</v>
+        <v>5.74303340911865</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.85347509384155</v>
+        <v>5.85347557067871</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>7.75</v>
       </c>
       <c r="G670" t="n">
-        <v>5.70621871948242</v>
+        <v>5.70621824264526</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>5.76512098312378</v>
+        <v>5.76512145996094</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G672" t="n">
-        <v>5.76512098312378</v>
+        <v>5.76512145996094</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>5.86083889007568</v>
+        <v>5.86083841323853</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>5.84611368179321</v>
+        <v>5.8461127281189</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G675" t="n">
-        <v>5.84611368179321</v>
+        <v>5.8461127281189</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G678" t="n">
-        <v>5.87556457519531</v>
+        <v>5.87556409835815</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>5.74303293228149</v>
+        <v>5.74303340911865</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G683" t="n">
-        <v>5.76512098312378</v>
+        <v>5.76512145996094</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G684" t="n">
-        <v>5.69149255752563</v>
+        <v>5.69149303436279</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G686" t="n">
-        <v>5.91237878799438</v>
+        <v>5.91237783432007</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G688" t="n">
-        <v>5.89765357971191</v>
+        <v>5.8976526260376</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>6.28788566589355</v>
+        <v>6.28788471221924</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>8.75</v>
       </c>
       <c r="G692" t="n">
-        <v>6.44250440597534</v>
+        <v>6.4425048828125</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.38360166549683</v>
+        <v>6.38360214233398</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>6.3688759803772</v>
+        <v>6.36887645721436</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G696" t="n">
-        <v>6.41305303573608</v>
+        <v>6.41305351257324</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G697" t="n">
-        <v>6.36151361465454</v>
+        <v>6.3615140914917</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>6.41305303573608</v>
+        <v>6.41305351257324</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G699" t="n">
-        <v>6.4572319984436</v>
+        <v>6.45723152160645</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G700" t="n">
-        <v>6.34678649902344</v>
+        <v>6.34678745269775</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G702" t="n">
-        <v>6.3688759803772</v>
+        <v>6.36887645721436</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>8.75</v>
       </c>
       <c r="G703" t="n">
-        <v>6.44250440597534</v>
+        <v>6.4425048828125</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G704" t="n">
-        <v>6.42041635513306</v>
+        <v>6.42041683197021</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G705" t="n">
-        <v>6.4719557762146</v>
+        <v>6.47195625305176</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G707" t="n">
-        <v>6.15535259246826</v>
+        <v>6.15535306930542</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20689392089844</v>
+        <v>6.20689296722412</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G709" t="n">
-        <v>6.22898197174072</v>
+        <v>6.22898149490356</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G710" t="n">
-        <v>6.08172464370728</v>
+        <v>6.08172559738159</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>6.28788566589355</v>
+        <v>6.28788471221924</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G714" t="n">
-        <v>6.39832735061646</v>
+        <v>6.3983268737793</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.35415077209473</v>
+        <v>6.35415029525757</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G716" t="n">
-        <v>6.37623834609985</v>
+        <v>6.37623929977417</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>8.5</v>
       </c>
       <c r="G717" t="n">
-        <v>6.2584342956543</v>
+        <v>6.25843286514282</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>8.5</v>
       </c>
       <c r="G718" t="n">
-        <v>6.2584342956543</v>
+        <v>6.25843286514282</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G719" t="n">
-        <v>6.08172464370728</v>
+        <v>6.08172559738159</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G721" t="n">
-        <v>6.03754711151123</v>
+        <v>6.03754758834839</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>6.22161912918091</v>
+        <v>6.22161865234375</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>6.04490995407104</v>
+        <v>6.04491090774536</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G725" t="n">
-        <v>6.15535259246826</v>
+        <v>6.15535306930542</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>6.22898197174072</v>
+        <v>6.22898149490356</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>6.10381269454956</v>
+        <v>6.10381317138672</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G729" t="n">
-        <v>6.28788566589355</v>
+        <v>6.28788471221924</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G730" t="n">
-        <v>6.49404382705688</v>
+        <v>6.49404525756836</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G731" t="n">
-        <v>6.3688759803772</v>
+        <v>6.36887645721436</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G732" t="n">
-        <v>6.47932004928589</v>
+        <v>6.47931909561157</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G734" t="n">
-        <v>6.55294704437256</v>
+        <v>6.55294752120972</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G735" t="n">
-        <v>6.55294704437256</v>
+        <v>6.55294752120972</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G736" t="n">
-        <v>6.4572319984436</v>
+        <v>6.45723152160645</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G737" t="n">
-        <v>6.42777967453003</v>
+        <v>6.42777919769287</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>6.35415077209473</v>
+        <v>6.35415029525757</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G740" t="n">
-        <v>6.10381269454956</v>
+        <v>6.10381317138672</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G744" t="n">
-        <v>6.36151361465454</v>
+        <v>6.3615140914917</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G747" t="n">
-        <v>6.32469844818115</v>
+        <v>6.32469940185547</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>6.28788566589355</v>
+        <v>6.28788471221924</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>6.22898197174072</v>
+        <v>6.22898149490356</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G750" t="n">
-        <v>6.18480443954468</v>
+        <v>6.18480491638184</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G754" t="n">
-        <v>6.17007875442505</v>
+        <v>6.17007923126221</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G757" t="n">
-        <v>6.01545906066895</v>
+        <v>6.01545858383179</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>6.03754711151123</v>
+        <v>6.03754758834839</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G759" t="n">
-        <v>6.18480443954468</v>
+        <v>6.18480491638184</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>6.10381269454956</v>
+        <v>6.10381317138672</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G761" t="n">
-        <v>6.13326501846313</v>
+        <v>6.13326406478882</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.5</v>
       </c>
       <c r="G763" t="n">
-        <v>6.2584342956543</v>
+        <v>6.25843286514282</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.75</v>
       </c>
       <c r="G765" t="n">
-        <v>6.44250440597534</v>
+        <v>6.4425048828125</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>6.41305303573608</v>
+        <v>6.41305351257324</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G767" t="n">
-        <v>6.52349519729614</v>
+        <v>6.52349615097046</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G768" t="n">
-        <v>6.47932004928589</v>
+        <v>6.47931909561157</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G769" t="n">
-        <v>6.56031084060669</v>
+        <v>6.56031036376953</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G770" t="n">
-        <v>6.60448837280273</v>
+        <v>6.60448741912842</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>6.58976173400879</v>
+        <v>6.58976221084595</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G773" t="n">
-        <v>6.64866542816162</v>
+        <v>6.64866495132446</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G774" t="n">
-        <v>6.60448837280273</v>
+        <v>6.60448741912842</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>6.66339159011841</v>
+        <v>6.66339063644409</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G776" t="n">
-        <v>6.64866542816162</v>
+        <v>6.64866495132446</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G777" t="n">
-        <v>6.56031084060669</v>
+        <v>6.56031036376953</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G778" t="n">
-        <v>6.61185073852539</v>
+        <v>6.61184978485107</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G779" t="n">
-        <v>6.64130210876465</v>
+        <v>6.64130258560181</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G780" t="n">
-        <v>6.61921262741089</v>
+        <v>6.61921310424805</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G781" t="n">
-        <v>6.70020484924316</v>
+        <v>6.70020532608032</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G782" t="n">
-        <v>6.7885594367981</v>
+        <v>6.78855991363525</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G783" t="n">
-        <v>6.7885594367981</v>
+        <v>6.78855991363525</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G785" t="n">
-        <v>6.73701906204224</v>
+        <v>6.73701953887939</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G786" t="n">
-        <v>6.73701906204224</v>
+        <v>6.73701953887939</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G787" t="n">
-        <v>6.84746217727661</v>
+        <v>6.84746265411377</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G788" t="n">
-        <v>6.89900159835815</v>
+        <v>6.89900302886963</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G789" t="n">
-        <v>6.9431791305542</v>
+        <v>6.94318008422852</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G790" t="n">
-        <v>6.90636539459229</v>
+        <v>6.90636491775513</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G794" t="n">
-        <v>6.88427686691284</v>
+        <v>6.88427639007568</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>9.75</v>
       </c>
       <c r="G795" t="n">
-        <v>7.17879152297974</v>
+        <v>7.17879056930542</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>7.14197731018066</v>
+        <v>7.14197778701782</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G797" t="n">
-        <v>7.12725067138672</v>
+        <v>7.12725114822388</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G798" t="n">
-        <v>6.9137282371521</v>
+        <v>6.91372871398926</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G799" t="n">
-        <v>6.9431791305542</v>
+        <v>6.94318008422852</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G801" t="n">
-        <v>6.92109060287476</v>
+        <v>6.9210901260376</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G802" t="n">
-        <v>7.03889751434326</v>
+        <v>7.03889656066895</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G803" t="n">
-        <v>7.01680850982666</v>
+        <v>7.01680755615234</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>9.5</v>
       </c>
       <c r="G804" t="n">
-        <v>6.9947190284729</v>
+        <v>6.99471950531006</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G805" t="n">
-        <v>6.9873571395874</v>
+        <v>6.98735570907593</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G806" t="n">
-        <v>6.9873571395874</v>
+        <v>6.98735570907593</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G807" t="n">
-        <v>6.95790481567383</v>
+        <v>6.95790433883667</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G808" t="n">
-        <v>7.12725067138672</v>
+        <v>7.12725114822388</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G809" t="n">
-        <v>7.16406536102295</v>
+        <v>7.16406393051147</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G810" t="n">
-        <v>7.21560478210449</v>
+        <v>7.21560621261597</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>7.21560478210449</v>
+        <v>7.21560621261597</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G812" t="n">
-        <v>7.21560478210449</v>
+        <v>7.21560621261597</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G813" t="n">
-        <v>7.27450752258301</v>
+        <v>7.27450799942017</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G814" t="n">
-        <v>7.31868553161621</v>
+        <v>7.31868505477905</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G815" t="n">
-        <v>7.32604885101318</v>
+        <v>7.32604837417603</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G816" t="n">
-        <v>7.52484655380249</v>
+        <v>7.52484512329102</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G817" t="n">
-        <v>7.52484655380249</v>
+        <v>7.52484512329102</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G818" t="n">
-        <v>7.56902170181274</v>
+        <v>7.56902265548706</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G819" t="n">
-        <v>7.42176485061646</v>
+        <v>7.42176532745361</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>7.23769378662109</v>
+        <v>7.23769283294678</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>7.29659700393677</v>
+        <v>7.29659795761108</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G825" t="n">
-        <v>7.28923368453979</v>
+        <v>7.28923463821411</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G826" t="n">
-        <v>7.34077453613281</v>
+        <v>7.34077405929565</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>7.33341121673584</v>
+        <v>7.33341026306152</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G831" t="n">
-        <v>7.25978231430054</v>
+        <v>7.2597827911377</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>7.23769378662109</v>
+        <v>7.23769283294678</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G834" t="n">
-        <v>7.25241947174072</v>
+        <v>7.25241994857788</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G835" t="n">
-        <v>7.25241947174072</v>
+        <v>7.25241994857788</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G836" t="n">
-        <v>7.23033142089844</v>
+        <v>7.23033094406128</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G837" t="n">
-        <v>7.25978231430054</v>
+        <v>7.2597827911377</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G838" t="n">
-        <v>7.25978231430054</v>
+        <v>7.2597827911377</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G840" t="n">
-        <v>7.48066759109497</v>
+        <v>7.48066854476929</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G841" t="n">
-        <v>7.67210292816162</v>
+        <v>7.6721019744873</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>7.65737819671631</v>
+        <v>7.65737724304199</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G843" t="n">
-        <v>7.65737819671631</v>
+        <v>7.65737724304199</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>7.65737819671631</v>
+        <v>7.65737724304199</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G845" t="n">
-        <v>8.0107946395874</v>
+        <v>8.01079559326172</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G849" t="n">
-        <v>7.93716478347778</v>
+        <v>7.93716669082642</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G856" t="n">
-        <v>7.69867467880249</v>
+        <v>7.69867420196533</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G857" t="n">
-        <v>7.69867467880249</v>
+        <v>7.69867420196533</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G858" t="n">
-        <v>7.80517816543579</v>
+        <v>7.80517911911011</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G859" t="n">
-        <v>7.72910499572754</v>
+        <v>7.72910404205322</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G862" t="n">
-        <v>7.78996419906616</v>
+        <v>7.78996324539185</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G863" t="n">
-        <v>7.72910499572754</v>
+        <v>7.72910404205322</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G869" t="n">
-        <v>7.59217071533203</v>
+        <v>7.59217119216919</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G870" t="n">
-        <v>7.69867467880249</v>
+        <v>7.69867420196533</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G872" t="n">
-        <v>7.68345975875854</v>
+        <v>7.6834602355957</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G873" t="n">
-        <v>7.74431848526001</v>
+        <v>7.74431896209717</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G875" t="n">
-        <v>7.82039308547974</v>
+        <v>7.82039213180542</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G876" t="n">
-        <v>7.72910499572754</v>
+        <v>7.72910404205322</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G877" t="n">
-        <v>7.72910499572754</v>
+        <v>7.72910404205322</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G880" t="n">
-        <v>7.6226019859314</v>
+        <v>7.62260103225708</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G881" t="n">
-        <v>7.74431848526001</v>
+        <v>7.74431896209717</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G882" t="n">
-        <v>7.80517816543579</v>
+        <v>7.80517911911011</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G883" t="n">
-        <v>8.15511894226074</v>
+        <v>8.15511798858643</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G884" t="n">
-        <v>8.21597671508789</v>
+        <v>8.21597766876221</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>11</v>
       </c>
       <c r="G885" t="n">
-        <v>8.36812496185303</v>
+        <v>8.36812400817871</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G887" t="n">
-        <v>7.92689609527588</v>
+        <v>7.92689561843872</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G891" t="n">
-        <v>7.9725399017334</v>
+        <v>7.97253942489624</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G892" t="n">
-        <v>8.03339958190918</v>
+        <v>8.0334005355835</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G893" t="n">
-        <v>7.92689609527588</v>
+        <v>7.92689561843872</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G894" t="n">
-        <v>8.12468910217285</v>
+        <v>8.12469005584717</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G895" t="n">
-        <v>7.92689609527588</v>
+        <v>7.92689561843872</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>7.91168117523193</v>
+        <v>7.91168165206909</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G897" t="n">
-        <v>7.94211101531982</v>
+        <v>7.94211149215698</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G898" t="n">
-        <v>7.91168117523193</v>
+        <v>7.91168165206909</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G899" t="n">
-        <v>7.89646625518799</v>
+        <v>7.89646768569946</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G904" t="n">
-        <v>8.185546875</v>
+        <v>8.18554782867432</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G905" t="n">
-        <v>7.94211101531982</v>
+        <v>7.94211149215698</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>7.91168117523193</v>
+        <v>7.91168165206909</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>7.91168117523193</v>
+        <v>7.91168165206909</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G911" t="n">
-        <v>7.78996419906616</v>
+        <v>7.78996324539185</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>7.75953435897827</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G914" t="n">
-        <v>7.78996419906616</v>
+        <v>7.78996324539185</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80517816543579</v>
+        <v>7.80517911911011</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G916" t="n">
-        <v>7.80517816543579</v>
+        <v>7.80517911911011</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G918" t="n">
-        <v>7.95732498168945</v>
+        <v>7.95732593536377</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G919" t="n">
-        <v>7.75953435897827</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G920" t="n">
-        <v>7.72910499572754</v>
+        <v>7.72910404205322</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G921" t="n">
-        <v>7.74431848526001</v>
+        <v>7.74431896209717</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G922" t="n">
-        <v>7.69867467880249</v>
+        <v>7.69867420196533</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G923" t="n">
-        <v>7.6226019859314</v>
+        <v>7.62260103225708</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G924" t="n">
-        <v>7.53131198883057</v>
+        <v>7.53131294250488</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G926" t="n">
-        <v>7.6226019859314</v>
+        <v>7.62260103225708</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G927" t="n">
-        <v>7.59977960586548</v>
+        <v>7.59977912902832</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G928" t="n">
-        <v>7.69867467880249</v>
+        <v>7.69867420196533</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G929" t="n">
-        <v>7.65303039550781</v>
+        <v>7.6530294418335</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G931" t="n">
-        <v>7.72910499572754</v>
+        <v>7.72910404205322</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G932" t="n">
-        <v>7.65303039550781</v>
+        <v>7.6530294418335</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G936" t="n">
-        <v>7.56934976577759</v>
+        <v>7.56934881210327</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G941" t="n">
-        <v>7.9725399017334</v>
+        <v>7.97253942489624</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G943" t="n">
-        <v>8.17033290863037</v>
+        <v>8.17033386230469</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>7.91168117523193</v>
+        <v>7.91168165206909</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G947" t="n">
-        <v>7.78996419906616</v>
+        <v>7.78996324539185</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G948" t="n">
-        <v>7.72910499572754</v>
+        <v>7.72910404205322</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G950" t="n">
-        <v>7.59217071533203</v>
+        <v>7.59217119216919</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G951" t="n">
-        <v>7.69867467880249</v>
+        <v>7.69867420196533</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G952" t="n">
-        <v>7.59977960586548</v>
+        <v>7.59977912902832</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G953" t="n">
-        <v>7.75953435897827</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>7.68345975875854</v>
+        <v>7.6834602355957</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G958" t="n">
-        <v>7.7747483253479</v>
+        <v>7.77474784851074</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G959" t="n">
-        <v>7.65303039550781</v>
+        <v>7.6530294418335</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G966" t="n">
-        <v>7.53131198883057</v>
+        <v>7.53131294250488</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G968" t="n">
-        <v>7.53131198883057</v>
+        <v>7.53131294250488</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>7.75953435897827</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>7.68345975875854</v>
+        <v>7.6834602355957</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G972" t="n">
-        <v>7.68345975875854</v>
+        <v>7.6834602355957</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>7.68345975875854</v>
+        <v>7.6834602355957</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>7.68345975875854</v>
+        <v>7.6834602355957</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>7.75953435897827</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>7.75953435897827</v>
+        <v>7.75953388214111</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G978" t="n">
-        <v>7.7747483253479</v>
+        <v>7.77474784851074</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G979" t="n">
-        <v>7.86603736877441</v>
+        <v>7.86603689193726</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G980" t="n">
-        <v>7.69867467880249</v>
+        <v>7.69867420196533</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G981" t="n">
-        <v>7.72910499572754</v>
+        <v>7.72910404205322</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G983" t="n">
-        <v>8.56591701507568</v>
+        <v>8.56591510772705</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G984" t="n">
-        <v>9.09843349456787</v>
+        <v>9.09843254089355</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G985" t="n">
-        <v>9.32665634155273</v>
+        <v>9.32665538787842</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>9.20493793487549</v>
+        <v>9.20493602752686</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G989" t="n">
-        <v>9.58530521392822</v>
+        <v>9.58530616760254</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>9.58530521392822</v>
+        <v>9.58530616760254</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G992" t="n">
-        <v>9.70702457427979</v>
+        <v>9.7070255279541</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G993" t="n">
-        <v>9.85917282104492</v>
+        <v>9.85917186737061</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>10.1938982009888</v>
+        <v>10.1938972473145</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.66138076782227</v>
+        <v>9.66137981414795</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.70702457427979</v>
+        <v>9.7070255279541</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1003" t="n">
-        <v>9.66138076782227</v>
+        <v>9.66137981414795</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.58530521392822</v>
+        <v>9.58530616760254</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.60052013397217</v>
+        <v>9.60052108764648</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.63094997406006</v>
+        <v>9.63095092773438</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1011" t="n">
-        <v>9.29622650146484</v>
+        <v>9.29622554779053</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.66138076782227</v>
+        <v>9.66137981414795</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.66138076782227</v>
+        <v>9.66137981414795</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1016" t="n">
-        <v>9.63094997406006</v>
+        <v>9.63095092773438</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1020" t="n">
-        <v>9.58530521392822</v>
+        <v>9.58530616760254</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1021" t="n">
-        <v>9.70702457427979</v>
+        <v>9.7070255279541</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.73745346069336</v>
+        <v>9.73745441436768</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1023" t="n">
-        <v>10.1786832809448</v>
+        <v>10.1786813735962</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1026" t="n">
-        <v>9.82874393463135</v>
+        <v>9.82874202728271</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1027" t="n">
-        <v>10.0569639205933</v>
+        <v>10.0569648742676</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1028" t="n">
-        <v>9.99610424041748</v>
+        <v>9.9961051940918</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>10.0113191604614</v>
+        <v>10.0113201141357</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1030" t="n">
-        <v>10.133038520813</v>
+        <v>10.1330375671387</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1031" t="n">
-        <v>10.3156147003174</v>
+        <v>10.3156156539917</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1033" t="n">
-        <v>10.3003997802734</v>
+        <v>10.3004007339478</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1034" t="n">
-        <v>10.3156147003174</v>
+        <v>10.3156156539917</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1035" t="n">
-        <v>10.3003997802734</v>
+        <v>10.3004007339478</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1036" t="n">
-        <v>10.2851858139038</v>
+        <v>10.2851867675781</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1038" t="n">
-        <v>10.3156147003174</v>
+        <v>10.3156156539917</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1039" t="n">
-        <v>10.330828666687</v>
+        <v>10.3308296203613</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1044" t="n">
-        <v>10.6959848403931</v>
+        <v>10.6959857940674</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1046" t="n">
-        <v>10.8329181671143</v>
+        <v>10.8329172134399</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1047" t="n">
-        <v>10.7720584869385</v>
+        <v>10.7720575332642</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1049" t="n">
-        <v>10.7872724533081</v>
+        <v>10.7872734069824</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>14</v>
       </c>
       <c r="G1051" t="n">
-        <v>10.6503400802612</v>
+        <v>10.6503410339355</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1053" t="n">
-        <v>9.76788425445557</v>
+        <v>9.76788330078125</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1054" t="n">
-        <v>9.82874393463135</v>
+        <v>9.82874202728271</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1058" t="n">
-        <v>9.02235984802246</v>
+        <v>9.02235889434814</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.26579666137695</v>
+        <v>9.26579570770264</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1062" t="n">
-        <v>8.71806335449219</v>
+        <v>8.71806526184082</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1063" t="n">
-        <v>8.29204845428467</v>
+        <v>8.29204940795898</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.82039308547974</v>
+        <v>7.82039213180542</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G1065" t="n">
-        <v>7.86603736877441</v>
+        <v>7.86603689193726</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1067" t="n">
-        <v>7.72910499572754</v>
+        <v>7.72910404205322</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1069" t="n">
-        <v>7.94211101531982</v>
+        <v>7.94211149215698</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1070" t="n">
-        <v>7.31830501556396</v>
+        <v>7.31830549240112</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.68345975875854</v>
+        <v>7.6834602355957</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.2726616859436</v>
+        <v>7.27266120910645</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>7.74431848526001</v>
+        <v>7.74431896209717</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1075" t="n">
-        <v>7.6226019859314</v>
+        <v>7.62260103225708</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1079" t="n">
-        <v>8.27683544158936</v>
+        <v>8.27683639526367</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>11.5</v>
       </c>
       <c r="G1080" t="n">
-        <v>8.74849319458008</v>
+        <v>8.74849414825439</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1082" t="n">
-        <v>9.02235984802246</v>
+        <v>9.02235889434814</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1083" t="n">
-        <v>8.83978366851807</v>
+        <v>8.83978271484375</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1085" t="n">
-        <v>9.02235984802246</v>
+        <v>9.02235889434814</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1087" t="n">
-        <v>9.20493793487549</v>
+        <v>9.20493602752686</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.71806335449219</v>
+        <v>8.71806526184082</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.62677478790283</v>
+        <v>8.62677669525146</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>11.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.74849319458008</v>
+        <v>8.74849414825439</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>11.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>8.74849319458008</v>
+        <v>8.74849414825439</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1095" t="n">
-        <v>8.65720462799072</v>
+        <v>8.65720558166504</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1097" t="n">
-        <v>8.83978366851807</v>
+        <v>8.83978271484375</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.88542747497559</v>
+        <v>8.88542652130127</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1100" t="n">
-        <v>8.79413890838623</v>
+        <v>8.79413795471191</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1102" t="n">
-        <v>8.94628524780273</v>
+        <v>8.94628620147705</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.70284843444824</v>
+        <v>8.70284938812256</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.83978366851807</v>
+        <v>8.83978271484375</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1107" t="n">
-        <v>8.74663162231445</v>
+        <v>8.74663066864014</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1108" t="n">
-        <v>8.43086910247803</v>
+        <v>8.43087100982666</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.25720024108887</v>
+        <v>8.25720119476318</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1111" t="n">
-        <v>8.92030048370361</v>
+        <v>8.92030143737793</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1113" t="n">
-        <v>8.50980854034424</v>
+        <v>8.50980949401855</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.46244716644287</v>
+        <v>8.46244621276855</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.71505546569824</v>
+        <v>8.71505641937256</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1132" t="n">
-        <v>9.89916610717773</v>
+        <v>9.89916706085205</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.0254735946655</v>
+        <v>10.0254716873169</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1136" t="n">
-        <v>9.94653224945068</v>
+        <v>9.94653129577637</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.5622692108154</v>
+        <v>10.5622682571411</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.5149040222168</v>
+        <v>10.5149030685425</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1142" t="n">
-        <v>10.4833269119263</v>
+        <v>10.4833278656006</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1144" t="n">
-        <v>10.5622692108154</v>
+        <v>10.5622682571411</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1145" t="n">
-        <v>10.5622692108154</v>
+        <v>10.5622682571411</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1147" t="n">
-        <v>10.3254470825195</v>
+        <v>10.3254461288452</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1148" t="n">
-        <v>10.4517517089844</v>
+        <v>10.4517526626587</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>13.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.6569986343384</v>
+        <v>10.6569976806641</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.8148794174194</v>
+        <v>10.8148803710938</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>14</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.051700592041</v>
+        <v>11.0517024993896</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.0990676879883</v>
+        <v>11.099066734314</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.1306438446045</v>
+        <v>11.1306419372559</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.0043382644653</v>
+        <v>11.004337310791</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>14</v>
       </c>
       <c r="G1160" t="n">
-        <v>11.051700592041</v>
+        <v>11.0517024993896</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1162" t="n">
-        <v>10.8780307769775</v>
+        <v>10.8780317306519</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>13.5</v>
       </c>
       <c r="G1165" t="n">
-        <v>10.6569986343384</v>
+        <v>10.6569976806641</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1166" t="n">
-        <v>10.89381980896</v>
+        <v>10.8938207626343</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1167" t="n">
-        <v>10.546480178833</v>
+        <v>10.5464811325073</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1168" t="n">
-        <v>10.2307186126709</v>
+        <v>10.2307176589966</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1172" t="n">
-        <v>10.3885984420776</v>
+        <v>10.3886003494263</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1173" t="n">
-        <v>10.499116897583</v>
+        <v>10.4991159439087</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1174" t="n">
-        <v>10.293869972229</v>
+        <v>10.2938709259033</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1175" t="n">
-        <v>10.4201755523682</v>
+        <v>10.4201745986938</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1176" t="n">
-        <v>10.3254470825195</v>
+        <v>10.3254461288452</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.3096599578857</v>
+        <v>10.3096590042114</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1179" t="n">
-        <v>10.3885984420776</v>
+        <v>10.3886003494263</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.2780818939209</v>
+        <v>10.2780828475952</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1183" t="n">
-        <v>10.2307186126709</v>
+        <v>10.2307176589966</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1185" t="n">
-        <v>10.0728368759155</v>
+        <v>10.0728378295898</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>13</v>
       </c>
       <c r="G1186" t="n">
-        <v>10.2622938156128</v>
+        <v>10.2622947692871</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>13</v>
       </c>
       <c r="G1187" t="n">
-        <v>10.2622938156128</v>
+        <v>10.2622947692871</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1190" t="n">
-        <v>10.2307186126709</v>
+        <v>10.2307176589966</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1191" t="n">
-        <v>10.3096599578857</v>
+        <v>10.3096590042114</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1192" t="n">
-        <v>10.4201755523682</v>
+        <v>10.4201745986938</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1193" t="n">
-        <v>10.4201755523682</v>
+        <v>10.4201745986938</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1194" t="n">
-        <v>10.5780563354492</v>
+        <v>10.5780572891235</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1195" t="n">
-        <v>10.3254470825195</v>
+        <v>10.3254461288452</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1197" t="n">
-        <v>10.6727857589722</v>
+        <v>10.6727867126465</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>13.5</v>
       </c>
       <c r="G1199" t="n">
-        <v>10.6569986343384</v>
+        <v>10.6569976806641</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1201" t="n">
-        <v>10.4833269119263</v>
+        <v>10.4833278656006</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1202" t="n">
-        <v>10.3570232391357</v>
+        <v>10.3570222854614</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1203" t="n">
-        <v>10.4675416946411</v>
+        <v>10.4675407409668</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1204" t="n">
-        <v>10.5622692108154</v>
+        <v>10.5622682571411</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1205" t="n">
-        <v>10.6412086486816</v>
+        <v>10.641209602356</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1206" t="n">
-        <v>10.6254224777222</v>
+        <v>10.6254234313965</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1207" t="n">
-        <v>10.5622692108154</v>
+        <v>10.5622682571411</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>13.5</v>
       </c>
       <c r="G1208" t="n">
-        <v>10.6569986343384</v>
+        <v>10.6569976806641</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1210" t="n">
-        <v>10.8148794174194</v>
+        <v>10.8148803710938</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1211" t="n">
-        <v>10.9411849975586</v>
+        <v>10.9411840438843</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1212" t="n">
-        <v>11.0043382644653</v>
+        <v>11.004337310791</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1213" t="n">
-        <v>10.8622436523438</v>
+        <v>10.8622446060181</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1214" t="n">
-        <v>10.9411849975586</v>
+        <v>10.9411840438843</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1215" t="n">
-        <v>11.2411594390869</v>
+        <v>11.2411584854126</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1216" t="n">
-        <v>11.0832767486572</v>
+        <v>11.0832786560059</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>14</v>
       </c>
       <c r="G1217" t="n">
-        <v>11.051700592041</v>
+        <v>11.0517024993896</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1218" t="n">
-        <v>10.6727857589722</v>
+        <v>10.6727867126465</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>10.9727611541748</v>
+        <v>10.9727602005005</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1221" t="n">
-        <v>10.6254224777222</v>
+        <v>10.6254234313965</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1225" t="n">
-        <v>10.4675416946411</v>
+        <v>10.4675407409668</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1227" t="n">
-        <v>9.69392108917236</v>
+        <v>9.69392013549805</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1232" t="n">
-        <v>10.1359901428223</v>
+        <v>10.1359882354736</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1234" t="n">
-        <v>10.6412086486816</v>
+        <v>10.641209602356</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1235" t="n">
-        <v>10.4201755523682</v>
+        <v>10.4201745986938</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1238" t="n">
-        <v>10.4359636306763</v>
+        <v>10.4359645843506</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1239" t="n">
-        <v>10.293869972229</v>
+        <v>10.2938709259033</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1240" t="n">
-        <v>10.4359636306763</v>
+        <v>10.4359645843506</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>13.5</v>
       </c>
       <c r="G1241" t="n">
-        <v>10.6569986343384</v>
+        <v>10.6569976806641</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>13.5</v>
       </c>
       <c r="G1243" t="n">
-        <v>10.6569986343384</v>
+        <v>10.6569976806641</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1244" t="n">
-        <v>10.6412086486816</v>
+        <v>10.641209602356</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1245" t="n">
-        <v>10.7833032608032</v>
+        <v>10.7833023071289</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1246" t="n">
-        <v>10.5149040222168</v>
+        <v>10.5149030685425</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>10.5780563354492</v>
+        <v>10.5780572891235</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>10.5780563354492</v>
+        <v>10.5780572891235</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1250" t="n">
-        <v>10.5622692108154</v>
+        <v>10.5622682571411</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1251" t="n">
-        <v>10.7043628692627</v>
+        <v>10.7043619155884</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1252" t="n">
-        <v>10.5780563354492</v>
+        <v>10.5780572891235</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1254" t="n">
-        <v>10.6727857589722</v>
+        <v>10.6727867126465</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1255" t="n">
-        <v>10.546480178833</v>
+        <v>10.5464811325073</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1256" t="n">
-        <v>10.499116897583</v>
+        <v>10.4991159439087</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1257" t="n">
-        <v>10.4201755523682</v>
+        <v>10.4201745986938</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1259" t="n">
-        <v>10.4833269119263</v>
+        <v>10.4833278656006</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1260" t="n">
-        <v>10.4201755523682</v>
+        <v>10.4201745986938</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1261" t="n">
-        <v>10.293869972229</v>
+        <v>10.2938709259033</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.3570232391357</v>
+        <v>10.3570222854614</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.4359636306763</v>
+        <v>10.4359645843506</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1264" t="n">
-        <v>10.5780563354492</v>
+        <v>10.5780572891235</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>13.5</v>
       </c>
       <c r="G1265" t="n">
-        <v>10.6569986343384</v>
+        <v>10.6569976806641</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1266" t="n">
-        <v>10.89381980896</v>
+        <v>10.8938207626343</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1267" t="n">
-        <v>10.89381980896</v>
+        <v>10.8938207626343</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1268" t="n">
-        <v>10.9253959655762</v>
+        <v>10.9253969192505</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>10.89381980896</v>
+        <v>10.8938207626343</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1271" t="n">
-        <v>10.8780307769775</v>
+        <v>10.8780317306519</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1272" t="n">
-        <v>10.9411849975586</v>
+        <v>10.9411840438843</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1273" t="n">
-        <v>10.7833032608032</v>
+        <v>10.7833023071289</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1274" t="n">
-        <v>10.7043628692627</v>
+        <v>10.7043619155884</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1276" t="n">
-        <v>10.6254224777222</v>
+        <v>10.6254234313965</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>13.5</v>
       </c>
       <c r="G1278" t="n">
-        <v>10.6569986343384</v>
+        <v>10.6569976806641</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1279" t="n">
-        <v>10.8780307769775</v>
+        <v>10.8780317306519</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1280" t="n">
-        <v>11.0201263427734</v>
+        <v>11.0201253890991</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1283" t="n">
-        <v>11.0990676879883</v>
+        <v>11.099066734314</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G1284" t="n">
-        <v>10.9885482788086</v>
+        <v>10.9885492324829</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1285" t="n">
-        <v>10.8780307769775</v>
+        <v>10.8780317306519</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1289" t="n">
-        <v>10.6727857589722</v>
+        <v>10.6727867126465</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1290" t="n">
-        <v>10.5780563354492</v>
+        <v>10.5780572891235</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.6727857589722</v>
+        <v>10.6727867126465</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>10.9727611541748</v>
+        <v>10.9727602005005</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1297" t="n">
-        <v>11.3674631118774</v>
+        <v>11.3674640655518</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>11.3674631118774</v>
+        <v>11.3674640655518</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>15</v>
       </c>
       <c r="G1303" t="n">
-        <v>11.8411092758179</v>
+        <v>11.8411083221436</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1304" t="n">
-        <v>11.5253458023071</v>
+        <v>11.5253467559814</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1305" t="n">
-        <v>11.6516513824463</v>
+        <v>11.6516523361206</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G1307" t="n">
-        <v>10.9885482788086</v>
+        <v>10.9885492324829</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1309" t="n">
-        <v>11.5095586776733</v>
+        <v>11.5095567703247</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.604287147522</v>
+        <v>11.6042861938477</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>15</v>
       </c>
       <c r="G1316" t="n">
-        <v>11.8411092758179</v>
+        <v>11.8411083221436</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>11.762167930603</v>
+        <v>11.7621688842773</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>11.9200506210327</v>
+        <v>11.9200496673584</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1319" t="n">
-        <v>12.0463542938232</v>
+        <v>12.0463552474976</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1320" t="n">
-        <v>12.1410837173462</v>
+        <v>12.1410827636719</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1322" t="n">
-        <v>12.1252956390381</v>
+        <v>12.1252946853638</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1323" t="n">
-        <v>12.1252956390381</v>
+        <v>12.1252946853638</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1324" t="n">
-        <v>12.519998550415</v>
+        <v>12.5199975967407</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>16</v>
       </c>
       <c r="G1325" t="n">
-        <v>12.6305170059204</v>
+        <v>12.6305160522461</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1326" t="n">
-        <v>12.519998550415</v>
+        <v>12.5199975967407</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1327" t="n">
-        <v>12.5989398956299</v>
+        <v>12.5989389419556</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1328" t="n">
-        <v>12.4884223937988</v>
+        <v>12.4884233474731</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1329" t="n">
-        <v>12.4252700805664</v>
+        <v>12.4252710342407</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1331" t="n">
-        <v>12.4252700805664</v>
+        <v>12.4252710342407</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1332" t="n">
-        <v>12.5042114257812</v>
+        <v>12.5042104721069</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>12.7883996963501</v>
+        <v>12.7883987426758</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>17</v>
       </c>
       <c r="G1338" t="n">
-        <v>13.4199228286743</v>
+        <v>13.4199237823486</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1339" t="n">
-        <v>13.6409568786621</v>
+        <v>13.6409587860107</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>17.5</v>
       </c>
       <c r="G1340" t="n">
-        <v>13.8146266937256</v>
+        <v>13.8146257400513</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1341" t="n">
-        <v>13.8462047576904</v>
+        <v>13.8462057113647</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1342" t="n">
-        <v>13.7988395690918</v>
+        <v>13.7988386154175</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1343" t="n">
-        <v>13.7988395690918</v>
+        <v>13.7988386154175</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1347" t="n">
-        <v>13.4830760955811</v>
+        <v>13.4830770492554</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1350" t="n">
-        <v>13.3883476257324</v>
+        <v>13.3883457183838</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>17</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.4199228286743</v>
+        <v>13.4199237823486</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1352" t="n">
-        <v>13.5935935974121</v>
+        <v>13.5935916900635</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1353" t="n">
-        <v>13.5462274551392</v>
+        <v>13.5462284088135</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1358" t="n">
-        <v>14.0514488220215</v>
+        <v>14.0514478683472</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1359" t="n">
-        <v>14.1320199966431</v>
+        <v>14.1320209503174</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1361" t="n">
-        <v>13.7452812194824</v>
+        <v>13.7452821731567</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1362" t="n">
-        <v>13.7291698455811</v>
+        <v>13.7291688919067</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1365" t="n">
-        <v>13.9547643661499</v>
+        <v>13.9547634124756</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1369" t="n">
-        <v>13.6647100448608</v>
+        <v>13.6647109985352</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1371" t="n">
-        <v>13.5841426849365</v>
+        <v>13.5841417312622</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1372" t="n">
-        <v>13.4068851470947</v>
+        <v>13.406886100769</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1375" t="n">
-        <v>13.6002540588379</v>
+        <v>13.6002550125122</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1381" t="n">
-        <v>13.7291698455811</v>
+        <v>13.7291688919067</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1384" t="n">
-        <v>13.9225387573242</v>
+        <v>13.9225378036499</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1386" t="n">
-        <v>13.7452812194824</v>
+        <v>13.7452821731567</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1388" t="n">
-        <v>13.6647100448608</v>
+        <v>13.6647109985352</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1394" t="n">
-        <v>13.5841426849365</v>
+        <v>13.5841417312622</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1398" t="n">
-        <v>13.7291698455811</v>
+        <v>13.7291688919067</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>13.9386491775513</v>
+        <v>13.9386501312256</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1403" t="n">
-        <v>13.9547643661499</v>
+        <v>13.9547634124756</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1408" t="n">
-        <v>13.7452812194824</v>
+        <v>13.7452821731567</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>13.7452812194824</v>
+        <v>13.7452821731567</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1411" t="n">
-        <v>13.6647100448608</v>
+        <v>13.6647109985352</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>13.5841426849365</v>
+        <v>13.5841417312622</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1416" t="n">
-        <v>13.7291698455811</v>
+        <v>13.7291688919067</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1417" t="n">
-        <v>13.6647100448608</v>
+        <v>13.6647109985352</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1420" t="n">
-        <v>14.2770442962646</v>
+        <v>14.277045249939</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1423" t="n">
-        <v>14.2609329223633</v>
+        <v>14.260931968689</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1427" t="n">
-        <v>14.6637830734253</v>
+        <v>14.6637840270996</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1430" t="n">
-        <v>14.6637830734253</v>
+        <v>14.6637840270996</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1431" t="n">
-        <v>14.7282400131226</v>
+        <v>14.7282390594482</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1432" t="n">
-        <v>14.7282400131226</v>
+        <v>14.7282390594482</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1433" t="n">
-        <v>14.4542999267578</v>
+        <v>14.4542989730835</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1434" t="n">
-        <v>14.9216070175171</v>
+        <v>14.9216060638428</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1435" t="n">
-        <v>15.2438869476318</v>
+        <v>15.2438879013062</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1442" t="n">
-        <v>14.679895401001</v>
+        <v>14.6798944473267</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1445" t="n">
-        <v>14.4542999267578</v>
+        <v>14.4542989730835</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1446" t="n">
-        <v>14.3898448944092</v>
+        <v>14.3898439407349</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1460" t="n">
-        <v>13.7291698455811</v>
+        <v>13.7291688919067</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1461" t="n">
-        <v>13.9386491775513</v>
+        <v>13.9386501312256</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1466" t="n">
-        <v>13.4552307128906</v>
+        <v>13.4552297592163</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1468" t="n">
-        <v>13.6002540588379</v>
+        <v>13.6002550125122</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1473" t="n">
-        <v>14.1320199966431</v>
+        <v>14.1320209503174</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1485" t="n">
-        <v>13.9869928359985</v>
+        <v>13.9869918823242</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1486" t="n">
-        <v>13.9869928359985</v>
+        <v>13.9869918823242</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1489" t="n">
-        <v>15.0182914733887</v>
+        <v>15.0182905197144</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1490" t="n">
-        <v>14.6637830734253</v>
+        <v>14.6637840270996</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1493" t="n">
-        <v>14.5832138061523</v>
+        <v>14.583212852478</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1494" t="n">
-        <v>14.4542999267578</v>
+        <v>14.4542989730835</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1498" t="n">
-        <v>13.9869928359985</v>
+        <v>13.9869918823242</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1500" t="n">
-        <v>13.6647100448608</v>
+        <v>13.6647109985352</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1502" t="n">
-        <v>13.9547643661499</v>
+        <v>13.9547634124756</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.6002540588379</v>
+        <v>13.6002550125122</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1504" t="n">
-        <v>13.5841426849365</v>
+        <v>13.5841417312622</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1511" t="n">
-        <v>13.7291698455811</v>
+        <v>13.7291688919067</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1515" t="n">
-        <v>13.1329469680786</v>
+        <v>13.1329479217529</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1524" t="n">
-        <v>13.5841426849365</v>
+        <v>13.5841417312622</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1525" t="n">
-        <v>13.6002540588379</v>
+        <v>13.6002550125122</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1529" t="n">
-        <v>13.6002540588379</v>
+        <v>13.6002550125122</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>13.2135181427002</v>
+        <v>13.2135190963745</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1532" t="n">
-        <v>12.7462100982666</v>
+        <v>12.7462110519409</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1533" t="n">
-        <v>12.9395780563354</v>
+        <v>12.9395790100098</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G1539" t="n">
-        <v>12.9234676361084</v>
+        <v>12.9234666824341</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1541" t="n">
-        <v>12.4239301681519</v>
+        <v>12.4239292144775</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>15</v>
       </c>
       <c r="G1542" t="n">
-        <v>12.0855350494385</v>
+        <v>12.0855340957642</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1544" t="n">
-        <v>12.3433589935303</v>
+        <v>12.3433599472046</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1545" t="n">
-        <v>12.0694208145142</v>
+        <v>12.0694217681885</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1546" t="n">
-        <v>12.230562210083</v>
+        <v>12.2305612564087</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1547" t="n">
-        <v>12.3433589935303</v>
+        <v>12.3433599472046</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1549" t="n">
-        <v>11.9888515472412</v>
+        <v>11.9888505935669</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1550" t="n">
-        <v>11.7149124145508</v>
+        <v>11.7149114608765</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1557" t="n">
-        <v>11.2637176513672</v>
+        <v>11.2637186050415</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1560" t="n">
-        <v>11.1992616653442</v>
+        <v>11.1992626190186</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1561" t="n">
-        <v>10.9897813796997</v>
+        <v>10.9897804260254</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1563" t="n">
-        <v>10.8930969238281</v>
+        <v>10.8930959701538</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1566" t="n">
-        <v>10.3613328933716</v>
+        <v>10.3613319396973</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1570" t="n">
-        <v>9.68454360961914</v>
+        <v>9.68454265594482</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1572" t="n">
-        <v>9.2816915512085</v>
+        <v>9.28169250488281</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1576" t="n">
-        <v>9.24946308135986</v>
+        <v>9.24946212768555</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1577" t="n">
-        <v>9.71677017211914</v>
+        <v>9.71676921844482</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1582" t="n">
-        <v>10.0068216323853</v>
+        <v>10.0068225860596</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1583" t="n">
-        <v>10.1840782165527</v>
+        <v>10.1840772628784</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1585" t="n">
-        <v>9.81345367431641</v>
+        <v>9.81345462799072</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1589" t="n">
-        <v>9.71677017211914</v>
+        <v>9.71676921844482</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1596" t="n">
-        <v>9.10443687438965</v>
+        <v>9.10443592071533</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>11</v>
       </c>
       <c r="G1599" t="n">
-        <v>8.86272525787354</v>
+        <v>8.86272621154785</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1602" t="n">
-        <v>9.15277862548828</v>
+        <v>9.15277767181396</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1604" t="n">
-        <v>9.49117374420166</v>
+        <v>9.49117279052734</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1606" t="n">
-        <v>9.2816915512085</v>
+        <v>9.28169250488281</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1607" t="n">
-        <v>9.15277862548828</v>
+        <v>9.15277767181396</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1608" t="n">
-        <v>9.24946308135986</v>
+        <v>9.24946212768555</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1614" t="n">
-        <v>9.63619995117188</v>
+        <v>9.63619899749756</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>6.42000007629395</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>96712</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>6.51000022888184</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>6.46999979019165</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>6.46999979019165</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>
